--- a/card_data.xlsx
+++ b/card_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E211"/>
+  <dimension ref="A1:E209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,877 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">### ,x %{s a s9i/}-look+
+bo&gt;'s h1d sitt+ on top (
+a well1 : seems puzzl+
+at f/1 b ! r1son = ?
+symbol is a matt} (
+leg5d4
+  ,"! 0 once1 leg5d has
+x1 a fe&gt;"s bo&gt;1 : liv$ 9
+a wood locat$ j |tside !
+manor ( ,brad=d4 ,a
+s|rce ( grt tr|ble to !
+</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">It shows a sinister-looking
+boar's head sitting on top of
+a well, which seems puzzling
+at first, but the reason for this
+symbol is a matter of
+legend.
+  There was once, legend has
+it, a fearsome boar, which lived in
+a wood located just outside the
+manor of Bradford. A
+source of great trouble to the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>01-04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### local folk ! bo&gt; was1
+br++ t}ror to ! p1ce;l
+flocks &amp; ravag+ !
+c.tryside &gt;.d4 ,ev5
+worse1 h{"e1 ! bo&gt; mo/
+lik$ to g to ! well t 0
+9 ! wood &amp; dr9k xs fre%
+wat}1 s t ! p ( ,brad=d
+_h second ?"|s ab visit+
+! well4 ,t ! p ( ,brad=d
+bore ! brunt ( ! b1/'s
+</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">local folk the boar was,
+bringing terror to the peaceful
+flocks and ravaging the
+countryside around. Even
+worse, however, the boar most
+liked to go to the well that was
+in the wood and drink its fresh
+water, so that the people of Bradford
+had second thoughts about visiting
+the well. That the people of Bradford
+bore the brunt of the beast's
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>01-05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### f}oc;y 0 unfair 9 ! eyes
+( ! p ( ! region4
+  ,ev5tually1 ! issue
+r1*$ ! e&gt;s ( ! k9dly ,"l
+( ! ,manor1 :o ! p _h
+(t5 ask$ = help4 ,! ,"l
+saw ! sev};y ( ! problem
+! p fac$ &amp; su7e/$ a 3te/
+cd solve ! problem4 ,he
+sd t :o"e cd kill ! bo&gt;
+&amp; br+ z pro( xs h1d to !
+</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ferocity was unfair in the eyes
+of the people of the region.
+  Eventually, the issue
+reached the ears of the kindly Lord
+of the Manor, who the people had
+often asked for help. The Lord
+saw the severity of the problem
+the people faced and suggested a contest
+could solve the problem. He
+said that whoever could kill the boar
+and bring as proof its head to the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>01-06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### ,manor ,h|se1 wd 2
+rew&gt;d$ ) l&amp; &amp; fame4 ,x 0
+! p ( ,brad=d &amp; ! p :o
+knew !m :o rjcd at ?
+proclama;n b "o "q
+rema9$3 :o wd kill !
+bo&gt;8
+  ,by ! h&amp;"s rew&gt;d _m
+felt tempt$1 b ! ?"| ( !
+bo&gt; ) xs d1dly tusks &amp;
+face l ?"u soon put an
+</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manor House, would be
+rewarded with land and fame. It was
+the people of Bradford and the people who
+knew them who rejoiced at this
+proclamation but one question
+remained: who would kill the
+boar?
+  By the handsome reward many
+felt tempted, but the thought of the
+boar with its deadly tusks and
+face like thunder soon put an
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>01-07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### 5d to _! ambi;ns4 ,h{"e1
+"! 0 "o huntsman :o 0 /
+wet 2h ! e&gt;s :o decid$ !
+prize 0 wor? a %ot 9
+spite ( ! bo&gt;'s
+reputa;n4
+  ,! huntsman 4cov}$ !
+bo&gt; pref}r$ to come | 9
+! middle ( ! "d4 ,s1 he
+w5t to ! wood by ! well
+) 8 gd b{1 to bide 8 "t4
+</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">end to their ambitions. However,
+there was one huntsman who was still
+wet behind the ears who decided the
+prize was worth a shot in
+spite of the boar's
+reputation.
+  The huntsman discovered the
+boar preferred to come out in
+the middle of the day. So, he
+went to the wood by the well
+with his good bow, to bide his time.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>01-08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">###   ,&gt;.d noon"t1 ! bo&gt;1
+fe&gt;$ by ! locals1 came |
+z sl{ z a snail f am;g !
+trees1 j z ! huntsman _h
+pr$ict$4 ,! huntsman
+l1p$ f 8 hid+ place &amp;1
+"? ! he&gt;t ) 8 f9e &gt;r{s1
+%ot ! bo&gt;4
+  ,n{ ! problem 0 no
+l;g} to kill ! bo&gt;4 ,x 0
+to f9d a way to c&gt;ry !
+</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Around noontime, the boar,
+feared by the locals, came out
+as slow as a snail from among the
+trees, just as the huntsman had
+predicted. The huntsman
+leaped from his hiding place and,
+through the heart with his fine arrows,
+shot the boar.
+  Now the problem was no
+longer to kill the boar. It was
+to find a way to carry the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>01-09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### bo&gt; back4 ,! h1d 0 too
+h1vy = ! ll huntsman to
+c&gt;ry back to ! ,manor
+,h|se1 b ! huntsman1 :o
+0 z qk-witt$ &amp; cunn+ z
+"e1 ask$ hmf1 8,:at else
+c ,i d to prove ,i kill$
+! bo&gt;80 ,! next 9/.e1 he
+op5$ ! bo&gt;'s m|? &amp; cut |
+xs t;gue1 tak+ t z pro(
+= ! ,"l4
+</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boar back. The head was too
+heavy for the little huntsman to
+carry back to the Manor
+House, but the huntsman, who
+was as quick-witted and cunning as
+ever, asked himself, "What else
+can I do to prove I killed
+the boar?" The next instance, he
+opened the boar's mouth and cut out
+its tongue, taking that as proof
+for the Lord.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>01-10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">###   ,he set | = ! ,manor
+,h|se z qkly z he cd1 &amp;
+he _h only be5 g"o a few
+m9utes :5 a second
+huntsman1 n s bold z !
+f/ b a ll m cunn+1 came
+on ! sc5e4
+  ,see+ ! sla9 c&gt;cass (
+! bo&gt;1 ! huntsman rjcd 9
+8 gd =tune4 ,! second
+huntsman knew a %ortcut
+</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  He set out for the Manor
+House as quickly as he could, and
+he had only been gone a few
+minutes when a second
+huntsman, not so bold as the
+first but a little more cunning, came
+on the scene.
+  Seeing the slain carcass of
+the boar, the huntsman rejoiced in
+his good fortune. The second
+huntsman knew a shortcut
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>01-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### to ! ,manor ,h|se 0 j
+&gt;.d ! ne&gt;by pond1 &amp;1 2+
+a bi7} man ?an ! f/1 0
+able to pick up ! bo&gt;'s
+h1d &amp; c&gt;ry x "? ! wood
+t{&gt;ds ! prize t await$
+hm4
+  ,! ,"l ( ! ,manor 0
+s1t$ 9 8 hall :5 !
+second huntsman bur/ "?
+! door &amp; 2gan to sp9 a
+</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to the Manor House was just
+around the nearby pond, and, being
+a bigger man than the first, was
+able to pick up the boar's
+head and carry it through the wood
+towards the prize that awaited
+him.
+  The Lord of the Manor was
+seated in his hall when the
+second huntsman burst through
+the door and began to spin a
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>01-12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### l9e4 8,! woes ( ,brad=d
+&gt;e 5d$60 he ann|nc$4 8,)
+my {n h&amp; ,i h sla9 !
+bo&gt;60 ,&amp;1 ) t1 at ! feet
+( 8 "l he dropp$ ! bo&gt;'s
+5orm|s h1d4
+  8,!n y w 2 rew&gt;d$1 z
+,i promis$4 ,b f/1 let
+me exam9e ! h1d ( ?
+mon/}10 sd ! ,"l ( !
+,manor4 ,to n exam9e !
+</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">line. "The woes of Bradford
+are ended!" he announced. "With
+my own hand I have slain the
+boar!" And, with that, at the feet
+of his lord he dropped the boar's
+enormous head.
+  "Then you will be rewarded, as
+I promised. But first, let
+me examine the head of this
+monster," said the Lord of the
+Manor. To not examine the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>01-13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### h1d 9 adv.e _h n be5 v
+cl"e on ! "p ( !
+huntsman4
+  ,"r away1 ! ,"l notic$
+! t;gue ( ! bo&gt; 0 miss+
+&amp; exclaim$1 8,:at is ?8
+,a bo&gt; ) no t;gue80 ,he
+look$ at ! huntsman
+dubi|sly4 8,h{ come ?
+cr1ture has no t;gue80
+he dem&amp;$4
+</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">head in advance had not been very
+clever on the part of the
+huntsman.
+  Right away, the Lord noticed
+the tongue of the boar was missing
+and exclaimed, "What is this?
+A boar with no tongue?" He
+looked at the huntsman
+dubiously. "How come this
+creature has no tongue?"
+he demanded.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>01-14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">###   ,all eyes 7 on !
+huntsman4 ,! huntsman
+"q$ by ! ,"l repli$1 8,i
+_c say1 my ,"l40 ,he 0
+sudd5ly r1liz+ 8 tricky
+situa;n cd 5d badly =
+hm4
+  ,"? ! door at ? mo;t1
+! f/ huntsman bur/4 8,!
+woes ( ,brad=d &gt;e 5d$60
+he cri$4 8,i h sla9 !
+</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  All eyes were on the
+huntsman. The huntsman
+questioned by the Lord replied, "I
+cannot say, my Lord." He was
+suddenly realizing his tricky
+situation could end badly for
+him.
+  Through the door at this moment,
+the first huntsman burst. "The
+woes of Bradford are ended!"
+he cried. "I have slain the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>01-15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### bo&gt; ! p ( ,brad=d
+dr1d$60
+  ,all eyes turn$ to !
+man :o n{ /ood 9 !
+doorway4 8,! rew&gt;d is
+alr giv510 sd ! ,"l ( !
+,manor4 8,! man "h has
+br"| to me ! bo&gt;'s h1d40
+  8,!n ": is xs t;gue80
+! f/ huntsman repli$4
+,&amp;1 s say+1 he drew | !
+</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boar the people of Bradford
+dreaded!"
+  All eyes turned to the
+man who now stood in the
+doorway. "The reward is
+already given," said the Lord of the
+Manor. "The man here has
+brought to me the boar's head."
+  "Then where is its tongue?"
+the first huntsman replied.
+And, so saying, he drew out the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>01-16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### bo&gt;'s t;gue he _h put 9
+8 hunt+ p|* &amp; relat$ h{
+he _h ambu%$ ! cr1ture 9
+! wood &amp; cut | xs t;gue
+z pro( ( 8 victory4
+  ,li/5+ to ! tale1 !
+,"l ( ! ,manor tri$ to
+4c}n : huntsman 0 tell+
+hm ! tru? &amp; :at ! two
+huntsm5 7 ?9k+ z !y
+wait$ = hm to make a
+</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boar's tongue he had put in
+his hunting pouch and related how
+he had ambushed the creature in
+the wood and cut out its tongue
+as proof of his victory.
+  Listening to the tale, the
+Lord of the Manor tried to
+discern which huntsman was telling
+him the truth and what the two
+huntsmen were thinking as they
+waited for him to make a
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>01-17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### deci.n4
+  ,alm 9/antly1 ! ,"l
+saw t ! second huntsman
+_h f$ hm a pack ( lies &amp;
+x 0 ! f/ huntsman :o 0 !
+true savior ( ,brad=d4
+,! ,"l 2liev$ ! second
+huntsman _h tri$ to /1l
+! f/ huntsman's prize &amp;
+s proclaim$ ! f/
+huntsman ! true victor4
+</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">decision.
+  Almost instantly, the Lord
+saw that the second huntsman
+had fed him a pack of lies and
+it was the first huntsman who was the
+true savior of Bradford.
+The Lord believed the second
+huntsman had tried to steal
+the first huntsman's prize and
+so proclaimed the first
+huntsman the true victor.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>01-18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### ,! ,"l wond}$ = a mo;t
+:y he alw 5c.t}$ s m*
+*ican}y 9 8 "ey"d
+9t}ac;ns4
+  ,! huntsman :o _h e&gt;n$
+8 prize fair &amp; squ&gt;e
+rcvd z 8 rew&gt;d a piece (
+l&amp; j |tside ! t{n1 "kn
+"!af z ,hunt ,y&gt;d4 ,8
+fame 0 9de$ assur$1 b x
+0 n ne&gt;ly z la/+ z t ( !
+</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Lord wondered for a moment
+why he always encountered so much
+chicanery in his everyday
+interactions.
+  The huntsman who had earned
+his prize fair and square
+received as his reward a piece of
+land just outside the town, known
+thereafter as Hunt Yard. His
+fame was indeed assured, but it
+was not nearly as lasting as that of the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>01-19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>### fe&gt;"s ,brad=d ,bo&gt;4</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>fearsome Bradford Boar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>01-01</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">###   ,if y 7 to j|rney to !
+,nor? ( ,5gl&amp;1 y wd come
+to a valley t is surr.d$
+by moors z hi&lt; z m.ta9s4
+,x is 9 ? valley ": y wd
+f9d ! c;y ( ,brad=d1 ":
+once a ?|s&amp; sp9n+-j5nies
+t humm$ &amp; clatt}$ spun
+wool 9to m"oy = !
+l;g-be&gt;d$ mill {n}s4 ,t
+all mill {n}s 7 g5}ally
+</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  If you were to journey to the
+North of England, you would come
+to a valley that is surrounded
+by moors as high as mountains.
+It is in this valley where you would
+find the city of Bradford, where
+once a thousand spinn±jennies
+that hummed and clattered spun
+wool into money for the
+long-bearded mill owners. That
+all mill owners were generally
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>01-02</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### busy z b1v}s &amp; q pl1s$ )
+!mvs = 2+ s su3ess;l &amp;
+well (f 0 "kn to !
+resid5ts ( ,brad=d1 &amp; if
+y 7 to g 9to ! c;y to
+visit ! /ately ,c;y
+,hall1 y wd see "! !
+,cre/ ( ! ,c;y (
+,brad=d1 : ~? same
+mill-{n}s cr1t$ to
+celebrate _! a*ieve;ts4
+</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busy as beavers and quite pleased with
+themselves for being so successful and
+well off was known to the
+residents of Bradford, and if
+you were to go into the city to
+visit the stately City
+Hall, you would see there the
+Crest of the City of
+Bradford, which those same
+mill-owners created to
+celebrate their achievements.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>01-03</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t xml:space="preserve">### ,x %{s a s9i/} look+
 bo&gt;'s h1d sitt+ on top (
 a well : seems puzzl+ at
@@ -579,7 +1450,7 @@
 </t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">It shows a sinister looking
 boar's head sitting on top of
@@ -596,21 +1467,21 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B24" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>01-04</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">### br++ t}ror to ! p1ce;l
 flocks &amp; ravag+ !
@@ -626,7 +1497,7 @@
 </t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">bringing terror to the peaceful
 flocks and ravaging the
@@ -643,21 +1514,21 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B25" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>01-05</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">### 0 unfair 9 ! eyes ( ! p
 ( ! region4 ,ev5tually1
@@ -673,7 +1544,7 @@
 </t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">was unfair in the eyes of the people
 of the region. Eventually,
@@ -690,21 +1561,21 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B26" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>01-06</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t xml:space="preserve">### ,h|se1 wd 2 rew&gt;d$ ) l&amp;
 &amp; fame4 ,x 0 ! p (
@@ -720,7 +1591,7 @@
 </t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t xml:space="preserve">House, would be rewarded with land
 and fame. It was the people of
@@ -737,21 +1608,21 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B27" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>01-07</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">### "! 0 "o huntsman1 :o 0 /
 wet 2h ! e&gt;s1 :o decid$
@@ -767,7 +1638,7 @@
 </t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">there was one huntsman, who was still
 wet behind the ears, who decided
@@ -784,21 +1655,21 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B28" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>01-08</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t xml:space="preserve">### fe&gt;$ by ! locals1 came
 |1 z sl{ z a snail1 f
@@ -814,7 +1685,7 @@
 </t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t xml:space="preserve">feared by the locals, came
 out, as slow as a snail, from
@@ -831,21 +1702,21 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B29" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>01-09</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t xml:space="preserve">###   ,! h1d 0 too h1vy = !
 ll huntsman to c&gt;ry back
@@ -861,7 +1732,7 @@
 </t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t xml:space="preserve">  The head was too heavy for the
 little huntsman to carry back
@@ -878,21 +1749,21 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B30" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>01-10</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t xml:space="preserve">### ,"l4
   ,he set | = ! ,manor
@@ -908,7 +1779,7 @@
 </t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t xml:space="preserve">Lord.
   He set out for the Manor
@@ -925,21 +1796,21 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B31" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>01-11</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t xml:space="preserve">### huntsman knew a %ortcut
 to ! ,manor ,h|se 0 j
@@ -955,7 +1826,7 @@
 </t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t xml:space="preserve">huntsman knew a shortcut
 to the Manor House was just
@@ -972,21 +1843,21 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B32" t="n">
         <v>12</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>01-12</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t xml:space="preserve">### ! door &amp; 2gan to sp9 a
 l9e4
@@ -1002,7 +1873,7 @@
 </t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t xml:space="preserve">the door and began to spin a
 line.
@@ -1019,21 +1890,21 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B33" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>01-13</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t xml:space="preserve">### mon/}10 sd ! ,"l ( !
 ,manor4
@@ -1049,7 +1920,7 @@
 </t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t xml:space="preserve">monster," said the Lord of the
 Manor.
@@ -1066,21 +1937,21 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B34" t="n">
         <v>14</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>01-14</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t xml:space="preserve">### come ? cr1ture has no
 t;gue80 he dem&amp;$4
@@ -1096,7 +1967,7 @@
 </t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t xml:space="preserve">come this creature has no
 tongue?" he demanded.
@@ -1113,21 +1984,21 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B35" t="n">
         <v>15</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>01-15</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t xml:space="preserve">### woes ( ,brad=d &gt;e 5d$60
 he cri$1 8,i h sla9 !
@@ -1143,7 +2014,7 @@
 </t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t xml:space="preserve">woes of Bradford are ended!"
 he cried, "I have slain the
@@ -1160,21 +2031,21 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B36" t="n">
         <v>16</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>01-16</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t xml:space="preserve">###   8,!n ": is xs t;gue80
 ! f/ huntsman repli$4
@@ -1190,7 +2061,7 @@
 </t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t xml:space="preserve">  "Then where is its tongue?"
 the first huntsman replied.
@@ -1207,21 +2078,21 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B37" t="n">
         <v>17</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>01-17</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t xml:space="preserve">### hm ! tru? &amp; :at ! two
 huntsm5 7 ?9k+ z !y
@@ -1237,7 +2108,7 @@
 </t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t xml:space="preserve">him the truth and what the two
 huntsmen were thinking as they
@@ -1254,21 +2125,21 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B38" t="n">
         <v>18</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>01-18</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t xml:space="preserve">### ! f/ huntsman's prize &amp;
 s proclaim$ ! f/
@@ -1284,7 +2155,7 @@
 </t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t xml:space="preserve">the first huntsman's prize and
 so proclaimed the first
@@ -1301,21 +2172,21 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B39" t="n">
         <v>19</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>01-19</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>### "!af z ,hunt ,y&gt;d4 ,8
 fame 0 9de$ assur$1 b x
@@ -1323,7 +2194,7 @@
 fe&gt;"s ,brad=d ,bo&gt;4</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>thereafter as Hunt Yard. His
 fame was indeed assured, but it
@@ -1332,883 +2203,6 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>01-01</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">###   ,if y 7 to j|rney to !
-,nor? ( ,5gl&amp;1 y wd come
-to a valley t is surr.d$
-by moors z hi&lt; z m.ta9s4
-,x is 9 ? valley ": y wd
-f9d ! c;y ( ,brad=d1 ":
-once a ?|s&amp; sp9n+-j5nies
-t humm$ &amp; clatt}$ spun
-wool 9to m"oy = !
-l;g-be&gt;d$ mill {n}s4 ,t
-all mill {n}s 7 g5}ally
-</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  If you were to journey to the
-North of England, you would come
-to a valley that is surrounded
-by moors as high as mountains.
-It is in this valley where you would
-find the city of Bradford, where
-once a thousand spinn±jennies
-that hummed and clattered spun
-wool into money for the
-long-bearded mill owners. That
-all mill owners were generally
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>01-02</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### busy z b1v}s &amp; q pl1s$ )
-!mvs = 2+ s su3ess;l &amp;
-well (f 0 "kn to !
-resid5ts ( ,brad=d1 &amp; if
-y 7 to g 9to ! c;y to
-visit ! /ately ,c;y
-,hall1 y wd see "! !
-,cre/ ( ! ,c;y (
-,brad=d1 : ~? same
-mill-{n}s cr1t$ to
-celebrate _! a*ieve;ts4
-</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busy as beavers and quite pleased with
-themselves for being so successful and
-well off was known to the
-residents of Bradford, and if
-you were to go into the city to
-visit the stately City
-Hall, you would see there the
-Crest of the City of
-Bradford, which those same
-mill-owners created to
-celebrate their achievements.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>01-03</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### ,x %{s a s9i/} look+
-bo&gt;'s h1d sitt+ on top (
-a well : seems puzzl+ at
-f/1 b ! r1son = ? symbol
-is a matt} ( leg5d4
-  ,"! 0 once1 leg5d has
-x1 a fe&gt;"s bo&gt;1 : liv$ 9
-a wood locat$ j |tside !
-manor ( ,brad=d4 ,a
-s|rce ( grt tr|ble to !
-local folk ! bo&gt; was1
-</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">It shows a sinister looking
-boar's head sitting on top of
-a well which seems puzzling at
-first, but the reason for this symbol
-is a matter of legend.
-  There was once, legend has
-it, a fearsome boar, which lived in
-a wood located just outside the
-manor of Bradford. A
-source of great trouble to the
-local folk the boar was,
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>01-04</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### br++ t}ror to ! p1ce;l
-flocks &amp; ravag+ !
-c.tryside &gt;.d4 ,ev5
-worse1 h{"e1 ! bo&gt; mo/
-lik$ to g to ! well t 0
-9 ! wood &amp; dr9k xs fre%
-wat}1 s t ! p ( ,brad=d
-_h second ?"|s ab visit+
-! well4
-  ,t ! p ( ,brad=d bore
-! brunt ( ! b1/'s f}oc;y
-</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bringing terror to the peaceful
-flocks and ravaging the
-countryside around. Even
-worse, however, the boar most
-liked to go to the well that was
-in the wood and drink its fresh
-water, so that the people of Bradford
-had second thoughts about visiting
-the well.
-  That the people of Bradford bore
-the brunt of the beast's ferocity
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>01-05</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### 0 unfair 9 ! eyes ( ! p
-( ! region4 ,ev5tually1
-! issue r1*$ ! e&gt;s ( !
-k9dly ,"l ( ! ,manor :o
-! p _h (t5 ask$ = help4
-  ,! ,"l saw ! sev};y (
-! problem ! p fac$ &amp;
-su7e/$ a 3te/ cd solve !
-problem4 ,he sd t :o"e
-cd kill ! bo&gt; &amp; br+ z
-pro( xs h1d to ! ,manor
-</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">was unfair in the eyes of the people
-of the region. Eventually,
-the issue reached the ears of the
-kindly Lord of the Manor who
-the people had often asked for help.
-  The Lord saw the severity of
-the problem the people faced and
-suggested a contest could solve the
-problem. He said that whoever
-could kill the boar and bring as
-proof its head to the Manor
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>01-06</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### ,h|se1 wd 2 rew&gt;d$ ) l&amp;
-&amp; fame4 ,x 0 ! p (
-,brad=d &amp; ! p :o knew !m
-:o rjcd at ? proclama;n
-b "o "q rema9$3 :o wd
-kill ! bo&gt;8
-  ,by ! h&amp;"s rew&gt;d _m
-felt tempt$1 b ! ?"| ( !
-bo&gt; ) xs d1dly tusks &amp;
-face l ?"u soon put an
-5d to _! ambi;ns4 ,h{"e1
-</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">House, would be rewarded with land
-and fame. It was the people of
-Bradford and the people who knew them
-who rejoiced at this proclamation
-but one question remained: who would
-kill the boar?
-  By the handsome reward many
-felt tempted, but the thought of the
-boar with its deadly tusks and
-face like thunder soon put an
-end to their ambitions. However,
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>7</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>01-07</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### "! 0 "o huntsman1 :o 0 /
-wet 2h ! e&gt;s1 :o decid$
-! prize 0 wor? a %ot 9
-spite ( ! bo&gt;'s
-reputa;n4
-  ,! huntsman 4cov}$ !
-bo&gt; pref}r$ to come | 9
-! middle ( ! "d4 ,s1 he
-w5t to ! wood by ! well
-) 8 gd b{1 to bide 8 "t4
-  ,&gt;.d noon"t1 ! bo&gt;1
-</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">there was one huntsman, who was still
-wet behind the ears, who decided
-the prize was worth a shot in
-spite of the boar's
-reputation.
-  The huntsman discovered the
-boar preferred to come out in
-the middle of the day. So, he
-went to the wood by the well
-with his good bow, to bide his time.
-  Around noontime, the boar,
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>8</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>01-08</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### fe&gt;$ by ! locals1 came
-|1 z sl{ z a snail1 f
-am;g ! trees1 j z !
-huntsman _h pr$ict$4 ,!
-huntsman l1p$ f 8 hid+
-place &amp; "? ! he&gt;t ) 8
-f9e &gt;r{s %ot ! bo&gt;4
-  ,n{ ! problem 0 no
-l;g} to kill ! bo&gt;4 ,x 0
-to f9d a way to c&gt;ry !
-bo&gt; back4
-</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">feared by the locals, came
-out, as slow as a snail, from
-among the trees, just as the
-huntsman had predicted. The
-huntsman leaped from his hiding
-place and through the heart with his
-fine arrows shot the boar.
-  Now the problem was no
-longer to kill the boar. It was
-to find a way to carry the
-boar back.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>9</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>01-09</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">###   ,! h1d 0 too h1vy = !
-ll huntsman to c&gt;ry back
-to ! ,manor ,h|se1 b !
-huntsman1 :o 0 z
-qk-witt$ &amp; cunn+ z "e1
-ask$ hmf1 8,:at else c
-,i d to prove ,i kill$ !
-bo&gt;80
-  ,! next 9/.e he op5$ !
-bo&gt;'s m|? &amp; cut | xs
-t;gue1 tak+ t z pro( = !
-</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  The head was too heavy for the
-little huntsman to carry back
-to the Manor House, but the
-huntsman, who was as
-quick-witted and cunning as ever,
-asked himself, "What else can
-I do to prove I killed the
-boar?"
-  The next instance he opened the
-boar's mouth and cut out its
-tongue, taking that as proof for the
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>10</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>01-10</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### ,"l4
-  ,he set | = ! ,manor
-,h|se z qkly z he cd &amp;
-he _h only be5 g"o a few
-m9utes :5 a second
-huntsman1 n s bold z !
-f/ b a ll m cunn+1 came
-on ! sc5e4
-  ,see+ ! sla9 c&gt;cass (
-! bo&gt;1 ! huntsman rjcd 9
-8 gd =tune4 ,! second
-</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lord.
-  He set out for the Manor
-House as quickly as he could and
-he had only been gone a few
-minutes when a second
-huntsman, not so bold as the
-first but a little more cunning, came
-on the scene.
-  Seeing the slain carcass of
-the boar, the huntsman rejoiced in
-his good fortune. The second
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>11</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>01-11</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### huntsman knew a %ortcut
-to ! ,manor ,h|se 0 j
-&gt;.d ! ne&gt;by pond1 &amp;1 2+
-a bi7} man ?an ! f/1 0
-able to pick up ! bo&gt;'s
-h1d &amp; c&gt;ry x "? ! wood
-t{&gt;ds ! prize t await$
-hm4
-  ,! ,"l ( ! ,manor 0
-s1t$ 9 8 hall :5 !
-second huntsman bur/ "?
-</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">huntsman knew a shortcut
-to the Manor House was just
-around the nearby pond, and, being
-a bigger man than the first, was
-able to pick up the boar's
-head and carry it through the wood
-towards the prize that awaited
-him.
-  The Lord of the Manor was
-seated in his hall when the
-second huntsman burst through
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>12</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>01-12</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### ! door &amp; 2gan to sp9 a
-l9e4
-  8,! woes ( ,brad=d &gt;e
-5d$60 he ann|nc$1 8,) my
-{n h&amp; ,i h sla9 ! bo&gt;60
-  ,&amp;1 ) t1 at ! feet ( 8
-"l he dropp$ ! bo&gt;'s
-5orm|s h1d4
-  8,!n y w 2 rew&gt;d$1 z
-,i promis$4 ,b f/1 let
-me exam9e ! h1d ( ?
-</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the door and began to spin a
-line.
-  "The woes of Bradford are
-ended!" he announced, "With my
-own hand I have slain the boar!"
-  And, with that, at the feet of his
-lord he dropped the boar's
-enormous head.
-  "Then you will be rewarded, as
-I promised. But first, let
-me examine the head of this
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>13</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>01-13</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### mon/}10 sd ! ,"l ( !
-,manor4
-  ,to n exam9e ! h1d 9
-adv.e _h n be5 v cl"e on
-! "p ( ! huntsman4
-  ,"r away1 ! ,"l notic$
-! t;gue ( ! bo&gt; 0 miss+
-&amp; exclaim$1 8,:at is ?8
-,a bo&gt; ) no t;gue80
-  ,he look$ at !
-huntsman1 dubi|sly4 8,h{
-</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">monster," said the Lord of the
-Manor.
-  To not examine the head in
-advance had not been very clever on
-the part of the huntsman.
-  Right away, the Lord noticed
-the tongue of the boar was missing
-and exclaimed, "What is this?
-A boar with no tongue?"
-  He looked at the
-huntsman, dubiously. "How
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>14</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>01-14</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### come ? cr1ture has no
-t;gue80 he dem&amp;$4
-  ,all eyes 7 on !
-huntsman4 ,! huntsman
-"q$ by ! ,"l repli$1 8,i
-_c say1 my ,"l40
-  ,he 0 sudd5ly r1liz+ 8
-tricky situa;n cd 5d
-badly = hm4
-  ,"? ! door at ? mo;t1
-! f/ huntsman bur/4 8,!
-</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">come this creature has no
-tongue?" he demanded.
-  All eyes were on the
-huntsman. The huntsman
-questioned by the Lord replied, "I
-cannot say, my Lord."
-  He was suddenly realizing his
-tricky situation could end
-badly for him.
-  Through the door at this moment,
-the first huntsman burst. "The
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>15</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>01-15</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### woes ( ,brad=d &gt;e 5d$60
-he cri$1 8,i h sla9 !
-bo&gt; ! p ( ,brad=d
-dr1d$60
-  ,all eyes turn$ to !
-man :o n{ /ood 9 !
-doorway4
-  8,! rew&gt;d is alr
-giv510 sd ! ,"l ( !
-,manor1 8,! man "h has
-br"| to me ! bo&gt;'s h1d40
-</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">woes of Bradford are ended!"
-he cried, "I have slain the
-boar the people of Bradford
-dreaded!"
-  All eyes turned to the
-man who now stood in the
-doorway.
-  "The reward is already
-given," said the Lord of the
-Manor, "The man here has
-brought to me the boar's head."
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>16</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>01-16</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">###   8,!n ": is xs t;gue80
-! f/ huntsman repli$4
-,&amp;1 s say+1 he drew | !
-bo&gt;'s t;gue he _h put 9
-8 hunt+ p|* &amp; relat$ h{
-he _h ambu%$ ! cr1ture 9
-! wood &amp; cut | xs t;gue
-z pro( ( 8 victory4
-  ,li/5+ to ! tale1 !
-,"l ( ! ,manor tri$ to
-4c}n : huntsman 0 tell+
-</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  "Then where is its tongue?"
-the first huntsman replied.
-And, so saying, he drew out the
-boar's tongue he had put in
-his hunting pouch and related how
-he had ambushed the creature in
-the wood and cut out its tongue
-as proof of his victory.
-  Listening to the tale, the
-Lord of the Manor tried to
-discern which huntsman was telling
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>17</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>01-17</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### hm ! tru? &amp; :at ! two
-huntsm5 7 ?9k+ z !y
-wait$ = hm to make a
-deci.n4
-  ,alm 9/antly1 ! ,"l
-saw t ! second huntsman
-_h f$ hm a pack ( lies &amp;
-x 0 ! f/ huntsman :o 0 !
-true savior ( ,brad=d4
-,! ,"l 2liev$ ! second
-huntsman _h tri$ to /1l
-</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">him the truth and what the two
-huntsmen were thinking as they
-waited for him to make a
-decision.
-  Almost instantly, the Lord
-saw that the second huntsman
-had fed him a pack of lies and
-it was the first huntsman who was the
-true savior of Bradford.
-The Lord believed the second
-huntsman had tried to steal
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>18</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>01-18</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### ! f/ huntsman's prize &amp;
-s proclaim$ ! f/
-huntsman ! true victor4
-,! ,"l wond}$ = a mo;t
-:y he alw 5c.t}$ s m*
-*ican}y 9 8 "ey"d
-9t}ac;ns4
-  ,! huntsman :o _h e&gt;n$
-8 prize fair &amp; squ&gt;e
-rcvd z 8 rew&gt;d a piece (
-l&amp; j |tside ! t{n1 "kn
-</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">the first huntsman's prize and
-so proclaimed the first
-huntsman the true victor.
-The Lord wondered for a moment
-why he always encountered so much
-chicanery in his everyday
-interactions.
-  The huntsman who had earned
-his prize fair and square
-received as his reward a piece of
-land just outside the town, known
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>19</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>01-19</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>### "!af z ,hunt ,y&gt;d4 ,8
-fame 0 9de$ assur$1 b x
-0 n ne&gt;ly z la/+ z t ( !
-fe&gt;"s ,brad=d ,bo&gt;4</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>thereafter as Hunt Yard. His
-fame was indeed assured, but it
-was not nearly as lasting as that of the
-fearsome Bradford Boar.</t>
-        </is>
-      </c>
-    </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -2225,33 +2219,33 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">###   ,a cle&gt; &amp; joy|s "d x 0
-&amp; | on ! wide1 op5 sea
-?|s&amp;s ~u ?|s&amp;s ( sp&gt;kl+
-wat}-drops excit$ by
-gett+ to play 9 ! oc1n
-d.ed all &gt;.d4 ,"o ( ~! 0
-a m}ry ll fell{ "nd
-,aqua :o d.ed on ! silv}
-backs ( ! fi%es z !y
-plung$ up &amp; d{n 9 !
-waves1 &amp;1 no matt} h{
+          <t xml:space="preserve">###   ,a cle&gt; &amp; joy|s "d x
+was1 &amp; | on ! wide op5
+sea1 ?|s&amp;s ~u ?|s&amp;s (
+sp&gt;kl+ wat} drops1
+excit$ by gett+ to play
+9 ! oc1n1 d.ed all &gt;.d4
+,"o ( ~! 0 a m}ry ll
+fell{ "nd ,aqua1 :o d.ed
+on ! silv} backs ( !
+fi%es z !y plung$ up &amp;
+d{n 9 ! waves1 &amp; no
 </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A clear and joyous day it was
-and out on the wide, open sea
-thousands upon thousands of sparkling
-water-drops excited by
-getting to play in the ocean
-danced all around. One of these was
-a merry little fellow named
-Aqua who danced on the silver
-backs of the fishes as they
-plunged up and down in the
-waves, and, no matter how
+          <t xml:space="preserve">  A clear and joyous day it
+was, and out on the wide open
+sea, thousands upon thousands of
+sparkling water drops,
+excited by getting to play
+in the ocean, danced all around.
+One of these was a merry little
+fellow named Aqua, who danced
+on the silver backs of the
+fishes as they plunged up and
+down in the waves, and no
 </t>
         </is>
       </c>
@@ -2272,32 +2266,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">### hi&lt; he sprung1 he alw
-came d{n ag 9to 8 "m's
-lap4 ,8 "m1 y "k1 0 !
-,oc1n1 &amp; v b1uti;l %e
+          <t xml:space="preserve">### matt} h{ hi&lt; he sprung1
+he alw came d{n ag 9to 8
+"m's lap4 ,8 "m1 y "k1 0
+! ,oc1n1 &amp; v b1uti;l %e
 look$ t summ} "d 9 h}
 d&gt;k blue dress &amp; :ite
 ru6les4
-  ,by &amp; by1 ! happy
-wat}-drop tir$ ( 8 play1
-&amp; look+ up to ! cle&gt; sky
+  ,by &amp; by1 ! happy wat}
+drop tir$ ( 8 play1 &amp;
+look+ up to ! cle&gt; sky
 abv hm1 ?"| he wd l to h
 </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">high he sprung, he always
-came down again into his mother's
-lap. His mother, you know, was the
-Ocean, and very beautiful she
+          <t xml:space="preserve">matter how high he sprung,
+he always came down again into his
+mother's lap. His mother, you know, was
+the Ocean, and very beautiful she
 looked that summer day in her
 dark blue dress and white
 ruffles.
-  By and by, the happy
-water-drop tired of his play,
-and looking up to the clear sky
+  By and by, the happy water
+drop tired of his play, and
+looking up to the clear sky
 above him, thought he would like to have
 </t>
         </is>
@@ -2319,7 +2313,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">### a sail on "o ( ! :ite1
+          <t xml:space="preserve">### a sail on "o ( ! :ite
 m&gt;%mall{-l cl|ds1 9/1d (
 sp5d+ 8 :ole life 9 !
 oc1n4 ,( ! sky1 ll ,aqua
@@ -2335,7 +2329,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">a sail on one of the white,
+          <t xml:space="preserve">a sail on one of the white
 marshmallow-like clouds, instead of
 spending his whole life in the
 ocean. Of the sky, little Aqua
@@ -2369,14 +2363,14 @@
           <t xml:space="preserve">### he acquiesc$ &amp; al took
 "e s _m o!r drops1 s t
 ,aqua mi&lt;t n 2 l"o"s on
-! way4
-  ,x 0 only ! sun t knew
-?1 h{"e1 = all ! o!r
-drops _h be5 *ang$ 9to
-f9e mi/ or vapor &amp; ,aqua
-cd n see !m4
+! way4 ,x 0 only ! sun t
+knew ?1 h{"e1 = all !
+o!r drops _h be5 *ang$
+9to f9e mi/ or vapor1 &amp;
+,aqua cd n see !m4
   ,d y "k :at vapor is8
-,if y br1! 9to ! air1 :5
+,if y br1! 9to ! air :5
+x is cold 5|&lt;1 y w see x
 </t>
         </is>
       </c>
@@ -2385,14 +2379,14 @@
           <t xml:space="preserve">he acquiesced and also took
 ever so many other drops, so that
 Aqua might not be lonesome on
-the way.
-  It was only the sun that knew
-this, however, for all the other
-drops had been changed into
-fine mist or vapor and Aqua
-could not see them.
+the way. It was only the sun that
+knew this, however, for all the
+other drops had been changed
+into fine mist or vapor, and
+Aqua could not see them.
   Do you know what vapor is?
-If you breathe into the air, when
+If you breathe into the air when
+it is cold enough, you will see it
 </t>
         </is>
       </c>
@@ -2413,33 +2407,33 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">### x is cold 5|&lt;1 y w see x
-com+ | ( yr m|? ?ick &amp;
+          <t xml:space="preserve">### com+ | ( yr m|? ?ick &amp;
 fa/ l /1m4 ,:5 ! vapor
 is q ne&gt; ! e&gt;?1 we call
-x 8fog04 ,9to vapor !
-wat} drops t d.ed 9 !
-oc1n _h be5 *ang$ 2c 9
-_! {n %ape !y 7 too h1vy
-= ! sunb1ms t ! sun let
-| to c&gt;ry4
-  ,hi&lt;} &amp; hi&lt;} !y sail$1
+x 8fog40
+  ,9to vapor1 ! wat}
+drops t d.ed 9 ! oc1n _h
+be5 *ang$1 2c1 9 _! {n
+%ape1 !y 7 too h1vy = !
+sunb1ms t ! sun let | to
+c&gt;ry4 ,hi&lt;} &amp; hi&lt;} !y
+sail$1 &amp; ?|&lt; x 0 gr&amp;1
 </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">it is cold enough, you will see it
-coming out of your mouth thick and
+          <t xml:space="preserve">coming out of your mouth thick and
 fast like steam. When the vapor
 is quite near the earth, we call
-it "fog". Into vapor the
-water drops that danced in the
-ocean had been changed because in
-their own shape they were too heavy
-for the sunbeams that the sun let
-out to carry.
-  Higher and higher they sailed,
+it "fog."
+  Into vapor, the water
+drops that danced in the ocean had
+been changed, because, in their own
+shape, they were too heavy for the
+sunbeams that the sun let out to
+carry. Higher and higher they
+sailed, and though it was grand,
 </t>
         </is>
       </c>
@@ -2460,33 +2454,33 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">### &amp; ?|&lt; x 0 gr&amp;1 ,aqua &amp; 8
-frs 7 l fi% | ( wat}1 s
-!y grew q dizzy4 ,!y
-5joy$ look+ d{n on ! _w
-2l1 :ile ! w9d scatt}$
-!m acr ! f|r corn}s ( !
-e&gt;?1 b af a :ile x grew
-ne&gt;ly "t = ! ,sun to g
-to b$4 ,he 2came v r$ 9
-! face1 &amp; 2gan to s9k
-l{} &amp; l{}1 until sudd5ly
+          <t xml:space="preserve">### ,aqua &amp; 8 frs 7 l fi% |
+( wat}1 s !y grew q
+dizzy4 ,!y 5joy$ look+
+d{n on ! _w 2l :ile !
+w9d scatt}$ !m acr ! f|r
+corn}s ( ! e&gt;?1 b af a
+:ile1 x grew ne&gt;ly "t =
+! ,sun to g to b$4 ,he
+2came v r$ 9 ! face1 &amp;
+2gan to s9k l{} &amp; l{}1
+until sudd5ly he w5t
 </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">and though it was grand, Aqua and his
-friends were like fish out of water, so
-they grew quite dizzy. They
-enjoyed looking down on the world
-below, while the wind scattered
-them across the four corners of the
-earth, but after a while it grew
-nearly time for the Sun to go
-to bed. He became very red in
-the face, and began to sink
-lower and lower, until suddenly
+          <t xml:space="preserve">Aqua and his friends were like fish out
+of water, so they grew quite
+dizzy. They enjoyed looking
+down on the world below while the
+wind scattered them across the four
+corners of the earth, but after a
+while, it grew nearly time for
+the Sun to go to bed. He
+became very red in the face, and
+began to sink lower and lower,
+until suddenly he went
 </t>
         </is>
       </c>
@@ -2507,13 +2501,13 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">### he w5t cle&gt; | ( si&lt;t6
-  ,poor ll ,aqua f"r5$
-by ! imp5d+ cold &amp; d&gt;k;s
-wi%$ he cd sleep n 9 !
-sky1 b "s": clos} to
-e&gt;?4 ,!n1 ,aqua he&gt;d !
-w9d bl{ &amp; 3jectur$ t
+          <t xml:space="preserve">### cle&gt; | ( si&lt;t6
+  ,poor ll ,aqua1 f"r5$
+by ! imp5d+ cold &amp;
+d&gt;k;s1 wi%$ he cd sleep1
+n 9 ! sky1 b "s": clos}
+to e&gt;?4 ,!n1 ,aqua he&gt;d
+! w9d bl{ &amp; 3jectur$ t
 maybe ! w9d cd take hm
 back d{n to ! oc1n4
   ,9de$1 ! w9d took p;y
@@ -2523,13 +2517,13 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">he went clear out of sight!
-  Poor little Aqua frightened
-by the impending cold and darkness
-wished he could sleep not in the
-sky, but somewhere closer to
-earth. Then, Aqua heard the
-wind blow and conjectured that
+          <t xml:space="preserve">clear out of sight!
+  Poor little Aqua, frightened
+by the impending cold and
+darkness, wished he could sleep,
+not in the sky, but somewhere closer
+to earth. Then, Aqua heard
+the wind blow and conjectured that
 maybe the wind could take him
 back down to the ocean.
   Indeed, the wind took pity
@@ -2558,7 +2552,7 @@
 9to a h1vy gray cl|d1 af
 : he blew !m a"p &amp; told
 !m to hurry d{n1 fa/ &amp;
-furi|s to ! e&gt;? s !y cd
+furi|s1 to ! e&gt;? s !y cd
 h a fi&lt;t+ *.e ( r1*+ !
 oc1n4 ,d{n !y w5t1 roll+
 ov} ea* o!r until ) a
@@ -2574,7 +2568,7 @@
 into a heavy gray cloud, after
 which he blew them apart and told
 them to hurry down, fast and
-furious to the earth so they could
+furious, to the earth so they could
 have a fighting chance of reaching the
 ocean. Down they went, rolling
 over each other until with a
@@ -2601,7 +2595,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">### cri$1 8,x's ra9+01 &amp;
+          <t xml:space="preserve">### cri$1 8,x's ra9+10 &amp;
 took | _! umbrellas4
   ,"s ( ! drops t 7 !
 mo/ =tunate1 9clud+
@@ -2617,7 +2611,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">cried, "It's raining", and
+          <t xml:space="preserve">cried, "It's raining," and
 took out their umbrellas.
   Some of the drops that were the
 most fortunate, including
@@ -2651,13 +2645,13 @@
           <t xml:space="preserve">### hillside1 until 9 !
 valley 2l !y he&gt;d !
 /range/ clatt}+ noise4
-,! ll wat}-drops 7 !n
-able to make | a
-fl|rmill t 0 /&amp;+ on !
-bank4 ,9side ! mill !
-wat}-drops saw two grt
-/"os1 : ! big :eel kept
-:izz+ r.d &amp; r.d4 ,! /"os
+,! ll wat} drops 7 !n
+able to make | a fl|r
+mill t 0 /&amp;+ on ! bank4
+,9side ! mill1 ! wat}
+drops saw two grt /"os1
+: ! big :eel kept :izz+
+r.d &amp; r.d4 ,! /"os1
 smoo!d by ! sp9n+1 7
 </t>
         </is>
@@ -2667,13 +2661,13 @@
           <t xml:space="preserve">hillside, until in the
 valley below they heard the
 strangest clattering noise.
-The little water-drops were then
-able to make out a
-flourmill that was standing on the
-bank. Inside the mill the
-water-drops saw two great
-stones, which the big wheel kept
-whizzing round and round. The stones
+The little water drops were then
+able to make out a flour
+mill that was standing on the bank.
+Inside the mill, the water
+drops saw two great stones,
+which the big wheel kept whizzing
+round and round. The stones,
 smoothed by the spinning, were
 </t>
         </is>
@@ -2699,13 +2693,13 @@
 fl|r &amp; ! corn 9to gold5
 m1l4 ,b :at giant d y
 suppose x 0 :o cd turn &amp;
-sw+ t trem5d|s :eel8
-  ,no giant at all4 ,x 0
-j |r t9y ll wat} drops1
-:o sprang on x by
-hundr$s &amp; ?|s&amp;s1 &amp; :irl$
-x ov} &amp; ov}4
-  ,x 0 lucky = !
+sw+ t trem5d|s :eel8 ,no
+giant at all4 ,x 0 j |r
+t9y ll wat} drops1 :o
+sprang on x by hundr$s &amp;
+?|s&amp;s1 &amp; :irl$ x ov} &amp;
+ov}4
+  ,x 0 lucky = ! wat}
 </t>
         </is>
       </c>
@@ -2715,13 +2709,13 @@
 flour and the corn into golden
 meal. But what giant do you
 suppose it was who could turn and
-swing that tremendous wheel?
-  No giant at all. It was
-just our tiny little water drops,
-who sprang on it by
-hundreds and thousands, and whirled
-it over and over.
-  It was lucky for the
+swing that tremendous wheel? No
+giant at all. It was just our
+tiny little water drops, who
+sprang on it by hundreds and
+thousands, and whirled it over and
+over.
+  It was lucky for the water
 </t>
         </is>
       </c>
@@ -2742,33 +2736,33 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">### wat}-drops t ! brook ":
-!y 7 swimm+ next empti$
-9to a b1uti;l pond ":
-ducks &amp; geese 7 liv+
-p1ce;lly4 ,aqua lik$ to
-play hide &amp; seek 9 ?
-pond1 &amp; x 0 8 bro!r wat}
-drop :o he fool$ by
-swimm+ to a big pool (
-wat} &amp; pret5d+ to hide
-"!1 b !n sn1k+ "u a rock
+          <t xml:space="preserve">### drops t ! brook ": !y 7
+swimm+ next empti$ 9to a
+b1uti;l pond ": ducks &amp;
+geese 7 liv+ p1ce;lly4
+,aqua lik$ to play hide
+&amp; seek 9 ? pond1 &amp; x 0 8
+bro!r wat} drop :o he
+fool$ by swimm+ to a big
+pool ( wat} &amp; pret5d+ to
+hide "!1 b !n sn1k+ "u a
+rock 9to an obscur$ ll
 </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">water-drops that the brook where
-they were swimming next emptied
-into a beautiful pond where
-ducks and geese were living
-peacefully. Aqua liked to
-play hide and seek in this
-pond, and it was his brother water
-drop who he fooled by
-swimming to a big pool of
-water and pretending to hide
-there, but then sneaking under a rock
+          <t xml:space="preserve">drops that the brook where they were
+swimming next emptied into a
+beautiful pond where ducks and
+geese were living peacefully.
+Aqua liked to play hide
+and seek in this pond, and it was his
+brother water drop who he
+fooled by swimming to a big
+pool of water and pretending to
+hide there, but then sneaking under a
+rock into an obscured little
 </t>
         </is>
       </c>
@@ -2789,9 +2783,8 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">### 9to an obscur$ ll
-puddle4 ,8 bro!r _h
-blatantly p1k$ &amp; ev5
+          <t xml:space="preserve">### puddle4 ,8 bro!r _h
+blatantly peek$ &amp; ev5
 foll{$ ,aqua z he 5t}$ !
 big pool ( wat}1 s :5 he
 se&gt;*$ "! &amp; cd n f9d hm1
@@ -2800,14 +2793,14 @@
 pond ": he cd play all
 "d1 s he /ay$ a gd :ile1
 sail+ up &amp; d{n1 tak+ !
+ducks' backs = %ips &amp; !
 </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">into an obscured little
-puddle. His brother had
-blatantly peaked and even
+          <t xml:space="preserve">puddle. His brother had
+blatantly peeked and even
 followed Aqua as he entered the
 big pool of water, so when he
 searched there and could not find him,
@@ -2816,6 +2809,7 @@
 pond where he could play all
 day, so he stayed a good while,
 sailing up and down, taking the
+ducks' backs for ships and the
 </t>
         </is>
       </c>
@@ -2836,33 +2830,33 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ducks' backs = %ips &amp; !
-frogs = horses1 b af a
+          <t xml:space="preserve">### frogs = horses1 b af a
 "t he tir$ ( ! dull
 life1 &amp; he &amp; 8 bro!rs
 float$ "u a bridge = a
 l;g 4t.e1 until !y saw
 ano!r brook tumbl+ d{n a
 hillside4
-  ,come1 let's jo9 h&amp;s6
-cri$ ,aqua &amp; 2c ! wat}
-drops 7 all tgr1 ov}com+
+  8,come1 let's jo9
+h&amp;s60 cri$ ,aqua1 &amp; 2c !
+wat} drops 7 all tgr1
+ov}com+ ! brook 0 *'s
 </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">ducks' backs for ships and the
-frogs for horses, but after a
+          <t xml:space="preserve">frogs for horses, but after a
 time he tired of the dull
 life, and he and his brothers
 floated under a bridge for a
 long distance, until they saw
 another brook tumbling down a
 hillside.
-  Come, let's join hands!
-cried Aqua and because the water
-drops were all together, overcoming
+  "Come, let's join
+hands!" cried Aqua, and because the
+water drops were all together,
+overcoming the brook was ch's
 </t>
         </is>
       </c>
@@ -2883,32 +2877,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ! brook 0 *'s play4 ,x 0
-by ! help ( ,aqua &amp; 8
-bro!rs t ! 2wit*+ riv} 0
-able to float h1vy %ips1
-?|&lt; n s l;g ago x 0 only
-a ll /r1m4 ,z ! riv}
-grew wid} &amp; he cd alm
-see ! oc1n1 ,aqua r1liz$
-8 j|rney 0 alm ov} &amp; he
-_h come full circle4
+          <t xml:space="preserve">### play4 ,x 0 by ! help (
+,aqua &amp; 8 bro!rs t !
+2wit*+ riv} 0 able to
+float h1vy %ips1 ?|&lt; n s
+l;g ago x 0 only a ll
+/r1m4 ,z ! riv} grew
+wid} &amp; he cd alm see !
+oc1n1 ,aqua r1liz$ 8
+j|rney 0 alm ov} &amp; he _h
+come full circle4
   ,back 9 ! oc1n1 he
 </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">the brook was ch's play. It was
-by the help of Aqua and his
-brothers that the bewitching river was
-able to float heavy ships,
-though not so long ago it was only
-a little stream. As the river
-grew wider and he could almost
-see the ocean, Aqua realized
-his journey was almost over and he
-had come full circle.
+          <t xml:space="preserve">play. It was by the help of
+Aqua and his brothers that the
+bewitching river was able to
+float heavy ships, though not so
+long ago it was only a little
+stream. As the river grew
+wider and he could almost see the
+ocean, Aqua realized his
+journey was almost over and he had
+come full circle.
   Back in the ocean, he
 </t>
         </is>
@@ -3005,8 +2999,8 @@
           <t xml:space="preserve">###   ,x 0 cold &amp; ne&gt;ly d&gt;k
 on ! la/ ev5+ ( ! old
 ye&gt;1 &amp; ! sn{ 0 fall+ fa/
-&amp; furi|s4 ,a ll girl no
-"o %elt}$ f ! gelid air
+&amp; furi|s4 ,a ll girl1 no
+"o %elt}$ f ! gelid air1
 roam$ "? ! /reets ) a
 b&gt;e h1d &amp; nak$ feet
 look+ z poor z a *ur*
@@ -3021,8 +3015,8 @@
           <t xml:space="preserve">  It was cold and nearly dark
 on the last evening of the old
 year, and the snow was falling fast
-and furious. A little girl no
-one sheltered from the gelid air
+and furious. A little girl, no
+one sheltered from the gelid air,
 roamed through the streets with a
 bare head and naked feet
 looking as poor as a church
@@ -3196,11 +3190,11 @@
 0 los+ /r5g? &amp; 2g9n+ to
 d|bt %e cd w1!r ? /orm4
 ,x 0 ,new ,ye&gt;'s &amp; !
-girl ask$ h}f :y z li&lt;ts
-%"o f e w9d{1 &amp; ! savory
-smell ( roa/ goose crept
-| on ! /reets1 %e 0
-|tside all al"o4
+girl ask$ h}f :y1 z
+li&lt;ts %"o f e w9d{ &amp; !
+savory smell ( roa/
+goose crept | on !
+/reets1 %e 0 |tside all
 </t>
         </is>
       </c>
@@ -3212,11 +3206,11 @@
 was losing strength and beginning to
 doubt she could weather this storm.
 It was New Year's and the
-girl asked herself why as lights
-shone from every window, and the savory
-smell of roast goose crept
-out on the streets, she was
-outside all alone.
+girl asked herself why, as
+lights shone from every window and the
+savory smell of roast
+goose crept out on the
+streets, she was outside all
 </t>
         </is>
       </c>
@@ -3237,12 +3231,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ,exhau/$1 %e f9ally sat
-d{n 9 a corn} 2h ! ll
-bak}y4 ,%e put a rag %e
-_h f.d ov} h} legs to
-cov} h}f1 b %e cd n keep
-(f ! cold4
+          <t xml:space="preserve">### al"o4 ,exhau/$1 %e
+f9ally sat d{n 9 a corn}
+2h ! ll bak}y4 ,%e put a
+rag %e _h f.d ov} h}
+legs to cov} h}f1 b %e
+cd n keep (f ! cold4
   ,! girl1 :o ! ni&lt;t air
 _h completely 5velop$1
 d&gt;$ n g home1 = %e _h
@@ -3253,12 +3247,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exhausted, she finally sat
-down in a corner behind the little
-bakery. She put a rag she
-had found over her legs to
-cover herself, but she could not keep
-off the cold.
+          <t xml:space="preserve">alone. Exhausted, she
+finally sat down in a corner
+behind the little bakery. She put a
+rag she had found over her
+legs to cover herself, but she
+could not keep off the cold.
   The girl, who the night air
 had completely enveloped,
 dared not go home, for she had
@@ -3294,7 +3288,7 @@
 !y _h only a pat*y ro(
 to cov} !m4
   ,! girl's ll h&amp;s 7 alm
-froz5 solid s %e decid$
+froz5 solid1 s %e decid$
 </t>
         </is>
       </c>
@@ -3310,7 +3304,7 @@
 they had only a patchy roof
 to cover them.
   The girl's little hands were almost
-frozen solid so she decided
+frozen solid, so she decided
 </t>
         </is>
       </c>
@@ -3525,11 +3519,11 @@
 sudd5ly %e saw a /&gt;
 fall1 l1v+ 2h x a b"r
 /r1k ( fire4
-  ,"s"o is dy+1 ?"| ! ll
-girl4
-  ,x 0 h} old gr&amp;"m1 !
-"o :o _h lov$ h} ! mo/1
-&amp; ! "o :o ! girl us$ to
+  8,"s"o is dy+10 ?"| !
+ll girl4 ,x 0 h} old
+gr&amp;"m1 ! "o :o _h lov$
+h} ! mo/1 &amp; ! "o :o !
+girl us$ to visit e
 </t>
         </is>
       </c>
@@ -3541,11 +3535,11 @@
 suddenly she saw a star
 fall, leaving behind it a bright
 streak of fire.
-  Someone is dying, thought the little
-girl.
-  It was her old grandmother, the
-one who had loved her the most,
-and the one who the girl used to
+  "Someone is dying," thought the
+little girl. It was her old
+grandmother, the one who had loved
+her the most, and the one who the
+girl used to visit every
 </t>
         </is>
       </c>
@@ -3566,9 +3560,9 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">### visit e ,sun"d1 :o _h
-told h} t :5 a /&gt; falls1
-a s|l l1ves ? e&gt;?4
+          <t xml:space="preserve">### ,sun"d1 :o _h told h} t
+:5 a /&gt; falls1 a s|l
+l1ves ? e&gt;?4
   ,x 0 h} la/ mat* t !
 ll girl n{ ru2$ on !
 wall &amp; ! li&lt;t ag %"o r.d
@@ -3582,9 +3576,9 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">visit every Sunday, who had
-told her that when a star falls,
-a soul leaves this earth.
+          <t xml:space="preserve">Sunday, who had told her that
+when a star falls, a soul
+leaves this earth.
   It was her last match that the
 little girl now rubbed on the
 wall and the light again shone round
@@ -3614,7 +3608,7 @@
       <c r="D70" t="inlineStr">
         <is>
           <t xml:space="preserve">###   8,gr&amp;"m10 cri$ ! ll
-"o1 8,o take me ) y6 ,i
+"o1 8,o1 take me ) y6 ,i
 "k y w g away :5 ! mat*
 burns |60
   ,! girl decid$ to li&lt;t
@@ -3630,7 +3624,7 @@
       <c r="E70" t="inlineStr">
         <is>
           <t xml:space="preserve">  "Grandmother," cried the little
-one, "O take me with you! I
+one, "O, take me with you! I
 know you will go away when the match
 burns out!"
   The girl decided to light
@@ -3795,12 +3789,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">###   ,once ~u a "t ! birds
+          <t xml:space="preserve">###   ,once ~u a "t1 ! birds
 took x 9to _! h1ds t !y
 wd l a ma/}1 &amp; t "o ( _!
 numb} m/ 2 *os5 k+4 ,a
 meet+ ( all ! birds 0
-call$ &amp; ?|&lt; !y "u/ood !
+call$1 &amp; ?|&lt; !y "u/ood !
 birds :o 7 f ! mo/ 4tant
 l&amp;s wd 2 unable to come1
 _m birds came f f&gt; away
@@ -3811,12 +3805,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Once upon a time the birds
+          <t xml:space="preserve">  Once upon a time, the birds
 took it into their heads that they
 would like a master, and that one of their
 number must be chosen king. A
 meeting of all the birds was
-called and though they understood the
+called, and though they understood the
 birds who were from the most distant
 lands would be unable to come,
 many birds came from far away
@@ -3845,14 +3839,14 @@
           <t xml:space="preserve">### hmf ! de facto k+1 &gt;riv$
 fa%ionably late4 ,x 0 a
 hawk :o 0 mo/ excit$ ab
-! meet+1 2c he 0 ! d&gt;k
+! meet+ 2c he 0 ! d&gt;k
 horse = k+4 ,! small fry
 came too1 &amp; ! rob91 !
 bluebird1 ! {l1 ! l&gt;k1 &amp;
 ! sp&gt;r{1 :o _h only a
 *.e 9 a million to 2 k+1
 7 all pres5t at ! meet+4
-,! cuckoo :o 0 alm n
+,! cuckoo1 :o 0 alm n
 </t>
         </is>
       </c>
@@ -3861,14 +3855,14 @@
           <t xml:space="preserve">himself the de facto king, arrived
 fashionably late. It was a
 hawk who was most excited about
-the meeting, because he was the dark
+the meeting because he was the dark
 horse for king. The small fry
 came too, and the robin, the
 bluebird, the owl, the lark, and
 the sparrow, who had only a
 chance in a million to be king,
 were all present at the meeting.
-The cuckoo who was almost not
+The cuckoo, who was almost not
 </t>
         </is>
       </c>
@@ -3891,8 +3885,8 @@
         <is>
           <t xml:space="preserve">### 9vit$ 2c 8 call s annoy$
 ! o!r birds1 came too4
-,x 0 ! v ll bird :o _h
-no "n at all1 h{"e t wd
+,x 0 ! v ll bird1 :o _h
+no "n at all1 h{"e1 t wd
 5d up ov}turn+ ! bal.e (
 p{} am;g ! birds4 ,t "!
 wd 2 grt 3fu.n &amp; noise
@@ -3907,8 +3901,8 @@
         <is>
           <t xml:space="preserve">invited because his call so annoyed
 the other birds, came too.
-It was the very little bird who had
-no name at all, however that would
+It was the very little bird, who had
+no name at all, however, that would
 end up overturning the balance of
 power among the birds. That there
 would be great confusion and noise
@@ -4038,9 +4032,9 @@
   ,! o!r birds gave | "o
 by "o &amp; :5 ! eagle saw ?
 he ?"|1 8,:at is ! use (
-fly+ any hi&lt;}8
-  ,? victory is 9 ! bag
-&amp; ,i am k+60
+fly+ any hi&lt;}8 ,?
+victory is 9 ! bag &amp; ,i
+am k+60
 </t>
         </is>
       </c>
@@ -4054,9 +4048,9 @@
   The other birds gave out one
 by one and when the eagle saw this
 he thought, "What is the use of
-flying any higher?
-  This victory is in the bag
-and I am king!"
+flying any higher? This
+victory is in the bag and I
+am king!"
 </t>
         </is>
       </c>
@@ -4133,8 +4127,8 @@
 &amp; !n fold+ 8 w+s tgr1 he
 sank to e&gt;? cry+ %rilly1
 8,i am k+6 ,i am k+60
-  ,! eagle trick$ by !
-ll bird _h n s5s$ ! bird
+  ,! eagle1 trick$ by !
+ll bird1 _h n s5s$ !
 </t>
         </is>
       </c>
@@ -4149,8 +4143,8 @@
 and then folding his wings together, he
 sank to earth crying shrilly,
 "I am king! I am king!"
-  The eagle tricked by the
-little bird had not sensed the bird
+  The eagle, tricked by the
+little bird, had not sensed the
 </t>
         </is>
       </c>
@@ -4171,8 +4165,8 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">### 9 8 f1!rs &amp; s _h n at
-all expect$ ! bird to
+          <t xml:space="preserve">### bird 9 8 f1!rs1 &amp; s _h n
+at all expect$ ! bird to
 come fly+ | l t4
   ,! birds back on e&gt;? 7
 all up 9 &gt;ms4
@@ -4187,8 +4181,8 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">in his feathers and so had not at
-all expected the bird to
+          <t xml:space="preserve">bird in his feathers, and so had not
+at all expected the bird to
 come flying out like that.
   The birds back on earth were
 all up in arms.
@@ -4218,14 +4212,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ov} u4
+          <t xml:space="preserve">### ov} u40
   ,! bird )|t a "n !n
 decid$ to cle&gt; ! air &amp;
 sd1 8,!n let "ey"o /&gt;t )
 a cl1n slate &amp; p}=m a
 new *all5g+ task4 ,!n we
 c decide :o %d 2 ! r1l
-k+43
+k+40
   ,!n ! birds ga!r$ tgr
 ag &amp; decid$ ! case wd 2
 resolv$ by mak+ a new
@@ -4234,14 +4228,14 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">over us.
+          <t xml:space="preserve">over us."
   The bird without a name then
 decided to clear the air and
 said, "Then let everyone start with
 a clean slate and perform a
 new challenging task. Then we
 can decide who should be the real
-king.:
+king."
   Then the birds gathered together
 again and decided the case would be
 resolved by making a new
@@ -4267,8 +4261,8 @@
         <is>
           <t xml:space="preserve">### 3di;n1 : 0 t he %d 2 k+
 :o cd g ! deepe/ 9to !
-e&gt;?4 ,s ! ll bird :o !
-o!r birds despis$ 0 n{
+e&gt;?4 ,s ! ll bird1 :o !
+o!r birds despis$1 0 n{
 back to squ&gt;e "o4
 ,3fid5t1 he rema9$1
 h{"e1 t if he play$ 8
@@ -4283,8 +4277,8 @@
         <is>
           <t xml:space="preserve">condition, which was that he should be king
 who could go the deepest into the
-earth. So the little bird who the
-other birds despised was now
+earth. So the little bird, who the
+other birds despised, was now
 back to square one.
 Confident, he remained,
 however, that if he played his
@@ -4359,33 +4353,33 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">### rema9+ birds :o ! ll/
-bird _h |twitt$ cri$ ag1
+          <t xml:space="preserve">### rema9+ birds1 :o ! ll/
+bird _h |twitt$1 cri$ ag
 ev5 m angrily ?an 2f1
 8,d y ?9k we wd rew&gt;d yr
 cunn+ 9 ? way8 ,no1 no6
 ,y % /ay 9 ! e&gt;? till y
 die ( hung}60
   ,s !y %ut up ! ll bird
-9 ! m|se's hole t ! m|se
-gave up mo/ unwill+ly1 &amp;
-bade ! {l wat* hm
+9 ! m|se's hole1 t !
+m|se gave up mo/
+unwill+ly1 &amp; bade ! {l
 </t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">remaining birds who the littlest
-bird had outwitted cried again,
+          <t xml:space="preserve">remaining birds, who the littlest
+bird had outwitted, cried again
 even more angrily than before,
 "Do you think we would reward your
 cunning in this way? No, no!
 You shall stay in the earth till you
 die of hunger!"
   So they shut up the little bird
-in the mouse's hole that the mouse
-gave up most unwillingly, and
-bade the owl watch him
+in the mouse's hole, that the
+mouse gave up most
+unwillingly, and bade the owl
 </t>
         </is>
       </c>
@@ -4406,7 +4400,8 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">### c&gt;e;lly ni&lt;t &amp; "d4
+          <t xml:space="preserve">### wat* hm c&gt;e;lly ni&lt;t &amp;
+"d4
   ,!n all ! birds w5t
 home to b$1 = !y 7 v
 tir$1 b ! {l assign$ by
@@ -4414,15 +4409,15 @@
 job 0 l"oly &amp; we&gt;i"s 2c
 he 0 j sitt+ al"o /&gt;+ at
 ! m|se's hole4
-  ,i c close "o eye &amp;
-wat* ) ! o!r1 he ?"|4
-  ,s he clos$ "o eye &amp;
+  8,i c close "o eye &amp;
+wat* ) ! o!r10 he ?"|4
 </t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">carefully night and day.
+          <t xml:space="preserve">watch him carefully night and
+day.
   Then all the birds went
 home to bed, for they were very
 tired, but the owl assigned by
@@ -4430,9 +4425,8 @@
 job was lonely and wearisome because
 he was just sitting alone staring at
 the mouse's hole.
-  I can close one eye and
-watch with the other, he thought.
-  So he closed one eye and
+  "I can close one eye and
+watch with the other," he thought.
 </t>
         </is>
       </c>
@@ -4453,7 +4447,8 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">### /&gt;$ /1dfa/ly ) ! o!r1 b
+          <t xml:space="preserve">###   ,s he clos$ "o eye &amp;
+/&gt;$ /1dfa/ly ) ! o!r1 b
 2f he knew x he =got to
 keep t "o op51 &amp; bo?
 eyes 7 fa/ asleep4 ,!n !
@@ -4463,13 +4458,13 @@
 he slipp$ f ! hole &amp;
 flew away4
   ,he want$ to %|t1 8,i
-am k+0 s t ! {l cd he&gt;
 </t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">stared steadfastly with the other, but
+          <t xml:space="preserve">  So he closed one eye and
+stared steadfastly with the other, but
 before he knew it he forgot to
 keep that one open, and both
 eyes were fast asleep. Then the
@@ -4479,7 +4474,6 @@
 he slipped from the hole and
 flew away.
   He wanted to shout, "I
-am king" so that the owl could hear
 </t>
         </is>
       </c>
@@ -4500,33 +4494,33 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">### hm z he flew1 b ?"|
+          <t xml:space="preserve">### am k+60 s t ! {l cd he&gt;
+hm z he flew1 b ?"|
 bett} ( x4
-  ,f ? "t on ! {l fool$
-by ! ll bird has n d&gt;$
-to %{ hmf by "d = fe&gt; !
-birds %d b1t ! liv+
-"dli&lt;ts | ( hm4 ,he
+  ,f ? "t on1 ! {l1
+fool$ by ! ll bird1 has
+n d&gt;$ to %{ hmf by "d =
+fe&gt; ! birds %d b1t !
+liv+ "dli&lt;ts | ( hm4 ,he
 flies ab only at
 ni&lt;t-"t1 hat+ &amp; pursu+ n
 ! bird1 b ! m|se = hav+
-made ! hole 9to : ! ll
 </t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">him as he flew, but thought
+          <t xml:space="preserve">am king!" so that the owl could hear
+him as he flew, but thought
 better of it.
-  From this time on the owl fooled
-by the little bird has not dared
-to show himself by day for fear the
-birds should beat the living
-daylights out of him. He
+  From this time on, the owl,
+fooled by the little bird, has
+not dared to show himself by day for
+fear the birds should beat the
+living daylights out of him. He
 flies about only at
 night-time, hating and pursuing not
 the bird, but the mouse for having
-made the hole into which the little
 </t>
         </is>
       </c>
@@ -4547,7 +4541,8 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">### bird crept4 ,&amp; ! ll bird
+          <t xml:space="preserve">### made ! hole 9to : ! ll
+bird crept4 ,&amp; ! ll bird
 al keeps | ( si&lt;t1 = he
 fe&gt;s t ! o!r birds %d
 puni% hm = 8 cunn+4 ,!
@@ -4557,13 +4552,13 @@
 slip away4
   ,he hides 9 ! h$ges1 &amp;
 :5 he ?9ks hmf q safe1
-he s+s |1 8,i am k+6 ,i
 </t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">bird crept. And the little bird
+          <t xml:space="preserve">made the hole into which the little
+bird crept. And the little bird
 also keeps out of sight, for he
 fears that the other birds should
 punish him for his cunning. The
@@ -4573,7 +4568,6 @@
 slip away.
   He hides in the hedges, and
 when he thinks himself quite safe,
-he sings out, "I am king! I
 </t>
         </is>
       </c>
@@ -4594,7 +4588,8 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>### am k+60
+          <t>### he s+s |1 8,i am k+6 ,i
+am k+60
   ,&amp; ! o!r birds 9
 mock}y call |1 8,yes1
 yes1 ! h$ge-k+6 !
@@ -4603,7 +4598,8 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>am king!"
+          <t>he sings out, "I am king! I
+am king!"
   And the other birds in
 mockery call out, "Yes,
 yes, the hedge-king! the
@@ -4634,10 +4630,10 @@
 ,he seem$ to 2 no di6}5t
 f ! re/ ( u4 ,he 0
 simply a man :o _h a
-h1d1 two &gt;ms &amp; two legs4
-,x m/ h be5 "s?+ pretty
-sup}lative t he _h hidd5
-away 2c he _h e "y girl
+h1d1 two &gt;ms1 &amp; two
+legs4 ,x m/ h be5 "s?+
+pretty sup}lative t he
+_h hidd5 away 2c he _h e
 </t>
         </is>
       </c>
@@ -4650,10 +4646,10 @@
 He seemed to be no different
 from the rest of us. He was
 simply a man who had a
-head, two arms and two legs.
-It must have been something pretty
-superlative that he had hidden
-away because he had every young girl
+head, two arms, and two
+legs. It must have been something
+pretty superlative that he
+had hidden away because he had every
 </t>
         </is>
       </c>
@@ -4674,8 +4670,8 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">### at ! orphanage wrapp$
-&gt;.d 8 ll f+}4
+          <t xml:space="preserve">### "y girl at ! orphanage
+wrapp$ &gt;.d 8 ll f+}4
   ,at ab n9e o'clock on
 ,satur"d morn+1 ,i
 figur$ a gd solu;n 0 to
@@ -4690,8 +4686,8 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">at the orphanage wrapped
-around his little finger.
+          <t xml:space="preserve">young girl at the orphanage
+wrapped around his little finger.
   At about nine o'clock on
 Saturday morning, I
 figured a good solution was to
@@ -4724,14 +4720,14 @@
           <t xml:space="preserve">### p}sonal;y1 b 8 wavy
 hair1 &amp; ! way he mov$ 8
 body4
-  ,ab a half an h|r
+  ,ab a half-an-h|r
 lat}1 ! boys 9 !
 orphanage call$ d{n to !
-ma9 d9+ room by ! matron
-7 told t !y 7 all go+ to
-d{nt{n ,jacksonville1
-,florida to get a new
-pair ( ,bu/} ,br{n %oes
+ma9 d9+ room by !
+matron1 7 told t !y 7
+all go+ to d{nt{n
+,jacksonville1 ,florida
+to get a new pair (
 </t>
         </is>
       </c>
@@ -4740,14 +4736,14 @@
           <t xml:space="preserve">personality, but his wavy
 hair, and the way he moved his
 body.
-  About a half an hour
+  About a half-an-hour
 later, the boys in the
 orphanage called down to the
-main dining room by the matron
-were told that they were all going to
-downtown Jacksonville,
-Florida to get a new
-pair of Buster Brown shoes
+main dining room by the
+matron, were told that they were
+all going to downtown
+Jacksonville, Florida
+to get a new pair of
 </t>
         </is>
       </c>
@@ -4768,33 +4764,33 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">### &amp; a hair cut4 ,t is :5
-,i got ? big idea1 : hit
-me l a ton ( bricks4 ,if
-! ,elvis haircut 0 ! big
+          <t xml:space="preserve">### ,bu/} ,br{n %oes &amp; a
+hair cut4 ,t is :5 ,i
+got ? big idea1 : hit me
+l a ton ( bricks4 ,if !
+,elvis haircut 0 ! big
 secret1 !n ,elvis's
 haircut ,i 0 go+ to get4
 ,i 0 go+ to h my "d 9 !
-sun1 &amp; all ! way to t{n
+sun1 &amp; all ! way to t{n1
 t 0 all ,i talk$ ab4 ,!
 fact t ,i 0 gett+ an
-,elvis haircut1 n j !
 </t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">and a hair cut. That is when
-I got this big idea, which hit
-me like a ton of bricks. If
-the Elvis haircut was the big
+          <t xml:space="preserve">Buster Brown shoes and a
+hair cut. That is when I
+got this big idea, which hit me
+like a ton of bricks. If the
+Elvis haircut was the big
 secret, then Elvis's
 haircut I was going to get.
 I was going to have my day in the
-sun, and all the way to town
+sun, and all the way to town,
 that was all I talked about. The
 fact that I was getting an
-Elvis haircut, not just the
 </t>
         </is>
       </c>
@@ -4815,7 +4811,8 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">### simple fact t we 7 gett+
+          <t xml:space="preserve">### ,elvis haircut1 n j !
+simple fact t we 7 gett+
 | ( ! orphanage1 made me
 "picul&gt;ly loquaci|s4 ,i
 told "eybody1 9clud+ !
@@ -4825,13 +4822,13 @@
 ,presley &amp; t ,i wd le&gt;n
 to move &gt;.d j l he did &amp;
 t ,i wd 2 ri* &amp; fam|s "o
-"d1 j l hm4 ,! matron
 </t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">simple fact that we were getting
+          <t xml:space="preserve">Elvis haircut, not just the
+simple fact that we were getting
 out of the orphanage, made me
 particularly loquacious. I
 told everybody, including the
@@ -4841,7 +4838,6 @@
 Presley and that I would learn
 to move around just like he did and
 that I would be rich and famous one
-day, just like him. The matron
 </t>
         </is>
       </c>
@@ -4862,7 +4858,8 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">### "u/ood my idea 0 "s?+ t
+          <t xml:space="preserve">### "d1 j l hm4 ,! matron
+"u/ood my idea 0 "s?+ t
 ,i 0 r1lly excit$ ab &amp;
 sd no?+4
   ,:5 ,i got my new
@@ -4872,13 +4869,13 @@
 b"rly1 &amp; ,i lik$ look+
 at ! b"os 9 my feet1 :
 ,i _h n"e se5 2f1 "? a
-special ;x-ray ma*9e !y
 </t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">understood my idea was something that
+          <t xml:space="preserve">day, just like him. The matron
+understood my idea was something that
 I was really excited about and
 said nothing.
   When I got my new
@@ -4888,7 +4885,6 @@
 brightly, and I liked looking
 at the bones in my feet, which
 I had never seen before, through a
-special x-ray machine they
 </t>
         </is>
       </c>
@@ -4909,7 +4905,8 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">### _h 9 ! %oe /ore t made !
+          <t xml:space="preserve">### special ;x-ray ma*9e !y
+_h 9 ! %oe /ore t made !
 b"os 9 yr feet look
 gre54 ,i 0 n{ alm r1dy
 to g back to ! orphanage
@@ -4919,13 +4916,13 @@
 %oes4 ,x 0 ! new
 haircut1 ?|&lt;1 t ,i ne$$
 to complete my new look4
-  ,we f9ally &gt;riv$ at !
 </t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">had in the shoe store that made the
+          <t xml:space="preserve">special x-ray machine they
+had in the shoe store that made the
 bones in your feet look
 green. I was now almost ready
 to go back to the orphanage
@@ -4935,7 +4932,6 @@
 shoes. It was the new
 haircut, though, that I needed
 to complete my new look.
-  We finally arrived at the
 </t>
         </is>
       </c>
@@ -4956,7 +4952,8 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">### unassum+1 unembelli%$
+          <t xml:space="preserve">###   ,we f9ally &gt;riv$ at !
+unassum+1 unembelli%$
 b&gt;b}%op1 ": !y cut |r
 hair = free 2c we 7
 orphans4 ,ev5 ?|&lt; we 7
@@ -4966,13 +4963,13 @@
 &amp; climb$ up onto ! bo&gt;d
 ! b&gt;b} plac$ acr ! &gt;ms
 to make me sit up hi&lt;}4
-  ,i look$ at ! man &amp;
 </t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">unassuming, unembellished
+          <t xml:space="preserve">  We finally arrived at the
+unassuming, unembellished
 barbershop, where they cut our
 hair for free because we were
 orphans. Even though we were
@@ -4982,7 +4979,6 @@
 and climbed up onto the board
 the barber placed across the arms
 to make me sit up higher.
-  I looked at the man and
 </t>
         </is>
       </c>
@@ -5003,7 +4999,8 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">### sd1 ) a b1m+ smile on my
+          <t xml:space="preserve">###   ,i look$ at ! man &amp;
+sd1 ) a b1m+ smile on my
 face1 8,i want an ,elvis
 haircut4 ,c y make my
 hair l ,elvis's80 ,i
@@ -5013,13 +5010,13 @@
 &amp; sd t he wd try 8 be/4
 ,i 0 s happy :5 he /&gt;t$
 to cut my hair1 b j z he
-/&gt;t$ to cut1 ! matron1
 </t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">said, with a beaming smile on my
+          <t xml:space="preserve">  I looked at the man and
+said, with a beaming smile on my
 face, "I want an Elvis
 haircut. Can you make my
 hair like Elvis's?" I
@@ -5029,7 +5026,6 @@
 and said that he would try his best.
 I was so happy when he started
 to cut my hair, but just as he
-started to cut, the matron,
 </t>
         </is>
       </c>
@@ -5050,33 +5046,33 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">### :o _h be5 wat*+ me &amp; _h
+          <t xml:space="preserve">### /&gt;t$ to cut1 ! matron1
+:o _h be5 wat*+ me &amp; _h
 a look z cold z ice1
 mo;n$ = hm to come ov}
 to ": %e 0 /&amp;+4 ,%e
 :isp}$ "s?+ 9to 8 e&gt; t
 caus$ ! b&gt;b} to %ake 8
 h1d1 l he 0 tell+ h}1
-8,no04 ,9 response1 !
+8,no40 ,9 response1 !
 matron walk$ ov} to a ll
 man sitt+ 9 an (fice
-*air t squ1k$ z x roll$
 </t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">who had been watching me and had
+          <t xml:space="preserve">started to cut, the matron,
+who had been watching me and had
 a look as cold as ice,
 motioned for him to come over
 to where she was standing. She
 whispered something into his ear that
 caused the barber to shake his
 head, like he was telling her,
-"No". In response, the
+"No." In response, the
 matron walked over to a little
 man sitting in an office
-chair that squeaked as it rolled
 </t>
         </is>
       </c>
@@ -5097,7 +5093,8 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">### &gt;.d ! floor &amp; spoke to
+          <t xml:space="preserve">### *air t squ1k$ z x roll$
+&gt;.d ! floor &amp; spoke to
 hm4 ,x 0 ! ll man :o !n
 walk$ ov} &amp; sd "s?+ to !
 man :o 0 cutt+ my hair4
@@ -5107,13 +5104,13 @@
 all{$ to give me an
 ,elvis cut4
   8,:y n80 ,i cri$
-desp}ately4
 </t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">around the floor and spoke to
+          <t xml:space="preserve">chair that squeaked as it rolled
+around the floor and spoke to
 him. It was the little man who then
 walked over and said something to the
 man who was cutting my hair.
@@ -5123,7 +5120,6 @@
 allowed to give me an
 Elvis cut.
   "Why not?" I cried
-desperately.
 </t>
         </is>
       </c>
@@ -5144,33 +5140,33 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">###   ,! k9dly b&gt;b} /opp$ by
-! matron did n answ}1 b
-f 8 expres.n1 ,i cd tell
-t he wi%$ he cd cut x z
-,i _h ask$4 ,)9 a few
-m9utes1 x wasn't an
-,elvis haircut1 b a %ort
-buzz cut t ! b&gt;b} _h
-giv5 me4 ,:5 he f9i%$
-%av+ (f all my hair &amp;
-made me smell r1l gd ) 8
+          <t xml:space="preserve">### desp}ately4
+  ,! k9dly b&gt;b}1 /opp$
+by ! matron1 did n
+answ}1 b f 8 expres.n1
+,i cd tell t he wi%$ he
+cd cut x z ,i _h ask$4
+,)9 a few m9utes1 x
+wasn't an ,elvis
+haircut1 b a %ort buzz
+cut t ! b&gt;b} _h giv5 me4
+,:5 he f9i%$ %av+ (f all
 </t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The kindly barber stopped by
-the matron did not answer, but
-from his expression, I could tell
-that he wished he could cut it as
-I had asked. Within a few
-minutes, it wasn't an
-Elvis haircut, but a short
-buzz cut that the barber had
-given me. When he finished
-shaving off all my hair and
-made me smell real good with his
+          <t xml:space="preserve">desperately.
+  The kindly barber, stopped
+by the matron, did not
+answer, but from his expression,
+I could tell that he wished he
+could cut it as I had asked.
+Within a few minutes, it
+wasn't an Elvis
+haircut, but a short buzz
+cut that the barber had given me.
+When he finished shaving off all
 </t>
         </is>
       </c>
@@ -5191,33 +5187,33 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">### p{d}1 ! b&gt;b} h&amp;$ me a
-nickel &amp; told me to g
-|tside to ! snack ma*9e
-&amp; buy myf a c&amp;y b&gt;4 ,i
-h&amp;$ hm ! nickel back &amp;
-told hm t ,i 0 n hungry4
+          <t xml:space="preserve">### my hair &amp; made me smell
+r1l gd ) 8 p{d}1 ! b&gt;b}
+h&amp;$ me a nickel &amp; told
+me to g |tside to !
+snack ma*9e &amp; buy myf a
+c&amp;y b&gt;4 ,i h&amp;$ hm !
+nickel back &amp; told hm t
+,i 0 n hungry4
   8,i'm s sorry1 baby10
-he sd1 z ,i climb$ | ( 8
+he sd z ,i climb$ | ( 8
 b&gt;b} *air4
-  8,i am n a baby10 ,i
-sd1 z ,i wip$ ! te&gt;s f
 </t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">powder, the barber handed me a
-nickel and told me to go
-outside to the snack machine
-and buy myself a candy bar. I
-handed him the nickel back and
-told him that I was not hungry.
+          <t xml:space="preserve">my hair and made me smell
+real good with his powder, the barber
+handed me a nickel and told
+me to go outside to the
+snack machine and buy myself a
+candy bar. I handed him the
+nickel back and told him that
+I was not hungry.
   "I'm so sorry, baby,"
-he said, as I climbed out of his
+he said as I climbed out of his
 barber chair.
-  "I am not a baby," I
-said, as I wiped the tears from
 </t>
         </is>
       </c>
@@ -5238,7 +5234,9 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">### my eyes4
+          <t xml:space="preserve">###   8,i am n a baby10 ,i
+sd1 z ,i wip$ ! te&gt;s f
+my eyes4
   ,i !n sat d{n on !
 floor &amp; bru%$ away !
 hair t _h a3umulat$ on
@@ -5247,14 +5245,14 @@
 9 ! cl|ds1 &amp; ,i got up
 (f ! floor1 bru%$ (f my
 %ort pants1 &amp; walk$
-sull5ly t{&gt;ds ! door4 ,!
-matron 0 smil+ at me
 </t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">my eyes.
+          <t xml:space="preserve">  "I am not a baby," I
+said, as I wiped the tears from
+my eyes.
   I then sat down on the
 floor and brushed away the
 hair that had accumulated on
@@ -5263,8 +5261,6 @@
 in the clouds, and I got up
 off the floor, brushed off my
 short pants, and walked
-sullenly towards the door. The
-matron was smiling at me
 </t>
         </is>
       </c>
@@ -5285,33 +5281,33 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">### sort ( funny l4
-  ,! b&gt;b} upset by !
-matron sd to h}1 8,y &gt;e
+          <t xml:space="preserve">### sull5ly t{&gt;ds ! door4 ,!
+matron 0 smil+ at me
+sort ( funny-l4
+  ,! b&gt;b}1 upset by !
+matron1 sd to h}1 8,y &gt;e
 j a damn bit*1 lady40
   ,%e yell$ back at hm
 at ! top ( h} lungs1 2f
 walk+ t{&gt;d ! (fice1 z
 fa/ z %e cd4 ,to %{ 8
 ang}1 ! man hit ! wall )
-8 h&amp; &amp; !n walk$ |tside
-": he /ood ag/ ! brick
 </t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">sort of funny like.
-  The barber upset by the
-matron said to her, "You are
+          <t xml:space="preserve">sullenly towards the door. The
+matron was smiling at me
+sort of funny-like.
+  The barber, upset by the
+matron, said to her, "You are
 just a damn bitch, lady."
   She yelled back at him
 at the top of her lungs, before
 walking toward the office, as
 fast as she could. To show his
 anger, the man hit the wall with
-his hand and then walked outside
-where he stood against the brick
 </t>
         </is>
       </c>
@@ -5332,33 +5328,33 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">### wall1 smok+ a cig&gt;ette4
+          <t xml:space="preserve">### 8 h&amp; &amp; !n walk$ |tside
+": he /ood ag/ ! brick
+wall1 smok+ a cig&gt;ette4
 ,i "u/ood "r "! my
 haircut 0 "s?+ t _h be5
-| ( ! p{} ( ! b&gt;b} &amp; !n
+| ( ! p{} ( ! b&gt;b}1 &amp; !n
 ,i sl{ly walk$ |tside to
 jo9 ! man4 ,he look$
 d{n1 smil$ at me1 &amp; !n
 he patt$ me on ! top (
 my bald z a coot h1d4 ,x
-0 a fact ( my life t ,i
-0 n gonna h hair t 0
 </t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">wall, smoking a cigarette.
+          <t xml:space="preserve">his hand and then walked outside
+where he stood against the brick
+wall, smoking a cigarette.
 I understood right there my
 haircut was something that had been
-out of the power of the barber and then
+out of the power of the barber, and then
 I slowly walked outside to
 join the man. He looked
 down, smiled at me, and then
 he patted me on the top of
 my bald as a coot head. It
-was a fact of my life that I
-was not gonna have hair that was
 </t>
         </is>
       </c>
@@ -5379,7 +5375,9 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>### any?+ l ,elvis's any"t
+          <t>### 0 a fact ( my life t ,i
+0 n gonna h hair t 0
+any?+ l ,elvis's any"t
 soon4
   ,i !n look$ up at !
 b&gt;b} ) my wet r$ eyes &amp;
@@ -5389,7 +5387,9 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>anything like Elvis's anytime
+          <t>was a fact of my life that I
+was not gonna have hair that was
+anything like Elvis's anytime
 soon.
   I then looked up at the
 barber with my wet red eyes and
@@ -5416,7 +5416,7 @@
         <is>
           <t xml:space="preserve">###   ,? is a /ory ( h{ ,mr4
 ,/icky got 9 ,a2y's fi%
-tank4 ,he's v small1
+tank4 8,he's v small10
 ,a2y's ,mom sd z %e pe}$
 at ! t9y wat} snail4
 ,a2y sd t he wd gr{ &amp; !n
@@ -5432,7 +5432,7 @@
         <is>
           <t xml:space="preserve">  This is a story of how Mr.
 Sticky got in Abby's fish
-tank. He's very small,
+tank. "He's very small,"
 Abby's Mom said as she peered
 at the tiny water snail.
 Abby said that he would grow and then
@@ -5510,15 +5510,15 @@
         <is>
           <t xml:space="preserve">### gravel4
   ,at s*ool t "d1 ,a2y1
-5c|rag$ by h} t1*} wrote
-excit$ly ab ! small &amp;
-my/}i|s ,mr4 ,/icky :o y
-cd mi/ake = a piece (
-gravel4 ,he seem$ an
-id1l pet = h} ,- "s ( !
-girls 9 h} class t1s$ ,-
-2c ,a2y 0 al v small4
-  ,t ev5+1 ,a2y turn$ on
+5c|rag$ by h} t1*}1
+wrote excit$ly ab !
+small &amp; my/}i|s ,mr4
+,/icky :o y cd mi/ake =
+a piece ( gravel4 ,he
+seem$ an id1l pet = h}
+,- "s ( ! girls 9 h}
+class t1s$ ,- 2c ,a2y 0
+al v small4
 </t>
         </is>
       </c>
@@ -5526,15 +5526,15 @@
         <is>
           <t xml:space="preserve">gravel.
   At school that day, Abby,
-encouraged by her teacher wrote
-excitedly about the small and
-mysterious Mr. Sticky who you
-could mistake for a piece of
-gravel. He seemed an
-ideal pet for her - some of the
-girls in her class teased -
-because Abby was also very small.
-  That evening, Abby turned on
+encouraged by her teacher,
+wrote excitedly about the
+small and mysterious Mr.
+Sticky who you could mistake for
+a piece of gravel. He
+seemed an ideal pet for her
+- some of the girls in her
+class teased - because Abby was
+also very small.
 </t>
         </is>
       </c>
@@ -5555,32 +5555,32 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ! li&lt;t &amp; f.d ,mr4 ,/icky
+          <t xml:space="preserve">###   ,t ev5+1 ,a2y turn$ on
+! li&lt;t &amp; f.d ,mr4 ,/icky
 cl++ to ! pondwe$ &amp; bo2+
 ab 9 ! air bu2les4
   8,t looks fun60 ,a2y
-exclaim$4
-  ,%e tri$ to imag9e :at
-x m/ 2 l to h to hang on
-to ?+s all "d &amp; decid$ !
-answ} 0 t x 0 probably v
-tir+4
+exclaim$4 ,%e tri$ to
+imag9e :at x m/ 2 l to h
+to hang on to ?+s all "d
+&amp; decid$ ! answ} 0 t x 0
+probably v tir+4
   ,a2y told h} ,mom t %e
 </t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">the light and found Mr. Sticky
+          <t xml:space="preserve">  That evening, Abby turned on
+the light and found Mr. Sticky
 clinging to the pondweed and bobbing
 about in the air bubbles.
   "That looks fun!" Abby
-exclaimed.
-  She tried to imagine what
-it must be like to have to hang on
-to things all day and decided the
-answer was that it was probably very
-tiring.
+exclaimed. She tried to
+imagine what it must be like to have
+to hang on to things all day
+and decided the answer was that it was
+probably very tiring.
   Abby told her Mom that she
 </t>
         </is>
@@ -5611,8 +5611,8 @@
   ,a2y :9$ t %e didn't
 want hm to get too big
 or he wdn't 2 cute
-anymore4
-  8,small ?+s1 n big ?+s
+anymore4 8,small ?+s1 n
+big ?+s1 &gt;e cute1 "r80
 </t>
         </is>
       </c>
@@ -5627,8 +5627,8 @@
   Abby whined that she didn't
 want him to get too big
 or he wouldn't be cute
-anymore.
-  "Small things, not big things
+anymore. "Small things, not
+big things, are cute, right?"
 </t>
         </is>
       </c>
@@ -5649,8 +5649,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">### &gt;e cute1 "r80 %e ask$1
-half to h}f4
+          <t xml:space="preserve">### %e ask$1 half to h}f4
   ,! next "d 9 &gt;t class1
 ,a2y ne$$ two pieces (
 pap} t 7 v exp5sive to
@@ -5660,13 +5659,13 @@
 pl1s$ ) ! draw+ &amp; want$
 x on ! wall4 ,! t1*}1 :o
 0 alw v 5c|rag+1 rem&gt;k$
+t ! draw+ ,a2y _h made 0
 </t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">are cute, right?" she asked,
-half to herself.
+          <t xml:space="preserve">she asked, half to herself.
   The next day in art class,
 Abby needed two pieces of
 paper that were very expensive to
@@ -5676,6 +5675,7 @@
 pleased with the drawing and wanted
 it on the wall. The teacher, who
 was always very encouraging, remarked
+that the drawing Abby had made was
 </t>
         </is>
       </c>
@@ -5696,33 +5696,33 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">### t ! draw+ ,a2y _h made 0
-v cr1tive &amp; b1m$ at
+          <t xml:space="preserve">### v cr1tive &amp; b1m$ at
 ,a2y1 giv+ h} ! s1l (
 approval4
   ,back at home1 ,mom1
 3v9c$ by ,a2y to cl1n |
-! tank 0 cl1n+ ) a
+! tank1 0 cl1n+ ) a
 special vacuum1 or
 8hoov}40
   8,":'s ,mr4 ,/icky80
-,a2y ask$ f/ ?+ :5 %e
+,a2y ask$ f/ ?+1 :5 %e
+came home f s*ool4
 </t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">that the drawing Abby had made was
-very creative and beamed at
+          <t xml:space="preserve">very creative and beamed at
 Abby, giving her the seal of
 approval.
   Back at home, Mom,
 convinced by Abby to clean out
-the tank was cleaning with a
+the tank, was cleaning with a
 special vacuum, or
 "hoover."
   "Where's Mr. Sticky?"
-Abby asked first thing when she
+Abby asked first thing, when she
+came home from school.
 </t>
         </is>
       </c>
@@ -5743,33 +5743,33 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">### came home f s*ool4
-  8,on ! side10 ,mom
+          <t xml:space="preserve">###   8,on ! side10 ,mom
 repli$4 ,&amp; !n %e add$1
-8,don't worry ,i w5t
+8,don't worry1 ,i w5t
 extra sl{ly s9ce x's
 bett} to 2 safe ?an
 sorry40
   ,a2y look$ on all
-sides ( ! tank b "! 0 no
-sign ( ! wat} snail t %e
-_h 4cov}$ a c|ple ( "ds
+sides ( ! tank1 b "! 0
+no sign ( ! wat} snail t
+%e _h 4cov}$ a c|ple (
+"ds ago4 ,%e 0 v sad4
 </t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">came home from school.
-  "On the side," Mom
+          <t xml:space="preserve">  "On the side," Mom
 replied. And then she added,
-"Don't worry I went
+"Don't worry, I went
 extra slowly since it's
 better to be safe than
 sorry."
   Abby looked on all
-sides of the tank but there was no
-sign of the water snail that she
-had discovered a couple of days
+sides of the tank, but there was
+no sign of the water snail that
+she had discovered a couple of
+days ago. She was very sad.
 </t>
         </is>
       </c>
@@ -5790,33 +5790,33 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ago4 ,%e 0 v sad4 ,h}
-,mom sd to wait a few
-h|rs until ! wat} cle&gt;s
-to take ano!r c&gt;e;l
-look4
+          <t xml:space="preserve">### ,h} ,mom sd to wait a
+few h|rs until ! wat}
+cle&gt;s to take ano!r
+c&gt;e;l look4
   ,t ev5+1 ,a2y w5t up
 to h} b$room to *eck !
 tank ag4 ,! wat} _h
-settl$ &amp; look$ cle&gt; b
+settl$ &amp; look$ cle&gt;1 b
 ,a2y cd n see ,mr4
 ,/icky4 ,a2y kneel$ d{n
+to h ano!r look 9 ! tank
 </t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">ago. She was very sad. Her
-Mom said to wait a few
-hours until the water clears
-to take another careful
-look.
+          <t xml:space="preserve">Her Mom said to wait a
+few hours until the water
+clears to take another
+careful look.
   That evening, Abby went up
 to her bedroom to check the
 tank again. The water had
-settled and looked clear but
+settled and looked clear, but
 Abby could not see Mr.
 Sticky. Abby kneeled down
+to have another look in the tank
 </t>
         </is>
       </c>
@@ -5837,33 +5837,33 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">### to h ano!r look 9 ! tank
-t h} ,mom _h cle&gt;$ s
+          <t xml:space="preserve">### t h} ,mom _h cle&gt;$ s
 ?or|&lt;ly1 b ,mr4 ,/icky 0
 / no": to 2 f.d4 ,a2y 0
 a bundle ( n}ves z %e
 desc5d$ ! /airs4 ,9 !
-/udy surr.d$ by books &amp;
-pap}s h} mom 0 "w+ &amp; %e
-look$ impati5t :5 %e saw
-,a2y 9 ! doorway &amp; ev5 m
-worri$ :5 %e he&gt;d ! bad
+/udy1 surr.d$ by books &amp;
+pap}s1 h} mom 0 "w+1 &amp;
+%e look$ impati5t :5 %e
+saw ,a2y 9 ! doorway &amp;
+ev5 m worri$ :5 %e he&gt;d
+! bad news4
 </t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">to have another look in the tank
-that her Mom had cleared so
+          <t xml:space="preserve">that her Mom had cleared so
 thoroughly, but Mr. Sticky was
 still nowhere to be found. Abby was
 a bundle of nerves as she
 descended the stairs. In the
-study surrounded by books and
-papers her mom was working and she
-looked impatient when she saw
-Abby in the doorway and even more
-worried when she heard the bad
+study, surrounded by books and
+papers, her mom was working, and
+she looked impatient when she
+saw Abby in the doorway and
+even more worried when she heard
+the bad news.
 </t>
         </is>
       </c>
@@ -5884,8 +5884,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">### news4
-  8,he'll turn up10 ,mom
+          <t xml:space="preserve">###   8,he'll turn up10 ,mom
 sd1 &amp; t 0 t4 ,!n1 to add
 fuel to ! flames1 %e
 rais$ h} t"o ( voice &amp;
@@ -5895,13 +5894,13 @@
 up on40
   ,a2y _h a qk temp} &amp;
 %e 0 angry z hell4
+8,y've hoov}$ hm up1
 </t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">news.
-  "He'll turn up," Mom
+          <t xml:space="preserve">  "He'll turn up," Mom
 said, and that was that. Then, to add
 fuel to the flames, she
 raised her tone of voice and
@@ -5911,6 +5910,7 @@
 up on."
   Abby had a quick temper and
 she was angry as hell.
+"You've hoovered him up,
 </t>
         </is>
       </c>
@@ -5931,33 +5931,33 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">###   8,y've hoov}$ hm up1
-hav5't y80 %e sd
+          <t xml:space="preserve">### hav5't y80 %e sd
 a3us+ly4
   ,a2y's ,mom d5i$
 ,a2y's v}.n ( ! /ory 0
 true &amp; sd t %e 0 c&gt;e;l1
-b 2c ,mr4 ,/icky 0 s
-small he 0 h&gt;d to see4
-  ,:at's wr;g ) 2+
-small8
+b1 2c ,mr4 ,/icky 0 s
+small1 he 0 h&gt;d to see4
+  8,:at's wr;g ) 2+
+small80
   8,no?+ at all1 b x
+makes ?+s h&gt;d to f9d40
 </t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">  "You've hoovered him up,
-haven't you?" she said
+          <t xml:space="preserve">haven't you?" she said
 accusingly.
   Abby's Mom denied
 Abby's version of the story was
 true and said that she was careful,
-but because Mr. Sticky was so
-small he was hard to see.
-  What's wrong with being
-small?
+but, because Mr. Sticky was so
+small, he was hard to see.
+  "What's wrong with being
+small?"
   "Nothing at all, but it
+makes things hard to find."
 </t>
         </is>
       </c>
@@ -5978,8 +5978,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">### makes ?+s h&gt;d to f9d40
-  8,or notice10 ,a2y sd1
+          <t xml:space="preserve">###   8,or notice10 ,a2y sd1
 sudd5ly feel+ l ! small1
 ov}look$ ,mr4 ,/icky h}f
 &amp; /orm+ f ! room4
@@ -5989,13 +5988,13 @@
 0 "! to try to make up =
 hav+ be5 9s5sitive
 e&gt;li}4 ,%e _h put h} "w
+on ! back burn} &amp; o3upi$
 </t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">makes things hard to find."
-  "Or notice," Abby said,
+          <t xml:space="preserve">  "Or notice," Abby said,
 suddenly feeling like the small,
 overlooked Mr. Sticky herself
 and storming from the room.
@@ -6005,6 +6004,7 @@
 was there to try to make up for
 having been insensitive
 earlier. She had put her work
+on the back burner and occupied
 </t>
         </is>
       </c>
@@ -6025,33 +6025,33 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">### on ! back burn} &amp; o3upi$
-h}f ) ,/icky4 ,a2y1 :o 0
+          <t xml:space="preserve">### h}f ) ,/icky4 ,a2y1 :o 0
 br1?+ fire all on a3.t (
 ! ll snail1 tri$ to
-ignore h} b x 0 h&gt;d :5
+ignore h}1 b x 0 h&gt;d :5
 ,mom walk$ ov} to ! b$ &amp;
 sat next to h}4 ,mom1 :o
 ,a2y / /ra9$ to rema9
 upset )1 _h g"o | to f9d
 h} glasses 9 ord} to
 se&gt;* = ,/icky m
+e6ectively4
 </t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">on the back burner and occupied
-herself with Sticky. Abby, who was
+          <t xml:space="preserve">herself with Sticky. Abby, who was
 breathing fire all on account of
 the little snail, tried to
-ignore her but it was hard when
+ignore her, but it was hard when
 Mom walked over to the bed and
 sat next to her. Mom, who
 Abby still strained to remain
 upset with, had gone out to find
 her glasses in order to
 search for Sticky more
+effectively.
 </t>
         </is>
       </c>
@@ -6072,33 +6072,33 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">### e6ectively4
-  8,? is my new &amp; extra
+          <t xml:space="preserve">###   8,? is my new &amp; extra
 p{};l pair ,i h =
-important o3a.ns l snail
-hunt+10 %e sd4
+important o3a.ns1 l
+snail hunt+10 %e sd4
   ,%e smil$ at ,a2y1
 try+ to butt} h} up1 b
 ,a2y didn't smile back4
 ,a2y 2liev$ h} mom's
 idea wd n su3e$1 b !n %e
 _h an idea ( h} {n4
+  8,i've got a magnify+
 </t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">effectively.
-  "This is my new and extra
+          <t xml:space="preserve">  "This is my new and extra
 powerful pair I have for
-important occasions like snail
-hunting," she said.
+important occasions, like
+snail hunting," she said.
   She smiled at Abby,
 trying to butter her up, but
 Abby didn't smile back.
 Abby believed her mom's
 idea would not succeed, but then she
 had an idea of her own.
+  "I've got a magnifying
 </t>
         </is>
       </c>
@@ -6119,8 +6119,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">###   ,i've got a magnify+
-glass1 ,a2y sudd5ly
+          <t xml:space="preserve">### glass10 ,a2y sudd5ly
 rememb}$ &amp; ru%$ (f to
 f9d x4
   ,on ! floor 2s ea* o!r
@@ -6130,13 +6129,13 @@
 corn}s am;g ! big pe2les
 &amp; ! pondwe$4 ,a2y tri$
 to imag9e1 if %e 7
+,/icky1 a ll wat} snail1
 </t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">  I've got a magnifying
-glass, Abby suddenly
+          <t xml:space="preserve">glass," Abby suddenly
 remembered and rushed off to
 find it.
   On the floor beside each other
@@ -6146,6 +6145,7 @@
 corners among the big pebbles
 and the pondweed. Abby tried
 to imagine, if she were
+Sticky, a little water snail,
 </t>
         </is>
       </c>
@@ -6166,33 +6166,33 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ,/icky1 a ll wat} snail1
-": wd %e hide |8 ,at "o
+          <t xml:space="preserve">### ": wd %e hide |8 ,at "o
 po9t %e ?"| %e saw hm1 b
 x wasn't ! wat} snail4
 ,x 0 a l&gt;ge speck ( du/
 t 0 deceptively bo2+ &gt;.d
-9 ! wat} l a live
+9 ! wat}1 l a live
 animal4
   ,!y 7 r1dy to call x
 quits1 :5 sudd5ly ,mom
-cri$1 8,ah ha60
+cri$1 8,ah ha60 ,tuck$ 9
+a curve ( ! &gt;*way1
 </t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sticky, a little water snail,
-where would she hide out? At one
+          <t xml:space="preserve">where would she hide out? At one
 point she thought she saw him, but
 it wasn't the water snail.
 It was a large speck of dust
 that was deceptively bobbing around
-in the water like a live
+in the water, like a live
 animal.
   They were ready to call it
 quits, when suddenly Mom
-cried, "Ah ha!"
+cried, "Ah ha!" Tucked in
+a curve of the archway,
 </t>
         </is>
       </c>
@@ -6213,10 +6213,9 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">###   ,tuck$ 9 a curve ( !
-&gt;*way1 p}fectly hidd5
-ag/ a pit* d&gt;k /"o1 sat
-,mr4 ,/icky1 safe &amp; s.d4
+          <t xml:space="preserve">### p}fectly hidd5 ag/ a
+pit* d&gt;k /"o1 sat ,mr4
+,/icky1 safe &amp; s.d4
   8,y1 ,i c alw c.t on10
 ,a2y sd to h} mom1 )
 relief4
@@ -6224,15 +6223,15 @@
 wat} snail 0 "r next to
 ,/icky &amp; ask$ ": ? new
 addi;n to ! family cd h
+come f4
 </t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Tucked in a curve of the
-archway, perfectly hidden
-against a pitch dark stone, sat
-Mr. Sticky, safe and sound.
+          <t xml:space="preserve">perfectly hidden against a
+pitch dark stone, sat Mr.
+Sticky, safe and sound.
   "You, I can always count on,"
 Abby said to her mom, with
 relief.
@@ -6240,6 +6239,7 @@
 water snail was right next to
 Sticky and asked where this new
 addition to the family could have
+come from.
 </t>
         </is>
       </c>
@@ -6260,33 +6260,33 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">### come f4
-  8,i'm 2g9n+ to suspect
+          <t xml:space="preserve">###   8,i'm 2g9n+ to suspect
 ! pond we$ is guilty1
 don't y ?9k80 repli$
 ,mom4
   ,!y bo? lau&lt;$ &amp; climb$
-9to ,a2y's b$ tgr &amp; ?|&lt;
+9to ,a2y's b$ tgr1 &amp; ?|&lt;
 x 0 cozy1 x 0 a bit ( a
 squeeze4
-  ,budge up1 ,mom sd1
+  8,budge up10 ,mom sd1
 giv+ ,a2y a pu% ) h}
+bottom4
 </t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">come from.
-  "I'm beginning to suspect
+          <t xml:space="preserve">  "I'm beginning to suspect
 the pond weed is guilty,
 don't you think?" replied
 Mom.
   They both laughed and climbed
-into Abby's bed together and though
+into Abby's bed together, and though
 it was cozy, it was a bit of a
 squeeze.
-  Budge up, Mom said,
+  "Budge up," Mom said,
 giving Abby a push with her
+bottom.
 </t>
         </is>
       </c>
@@ -6307,27 +6307,29 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>### bottom4 8,i c't 2c ,i'm
-alr on ! $ge4 ,gd h1v5s1
-y've gr{n !n4 ,:5 did t
-happ58 ,y cd've put an
-elephant 9 "h la/ "t we
-did ?4 ,2f ,i "k x1 y'll
-2 all gr{n up40
-  ,on h} mom's *e/ ,a2y
+          <t>###   8,i c't 2c ,i'm alr on
+! $ge40
+  8,gd h1v5s1 y've gr{n
+!n4 ,:5 did t happ58 ,y
+cd've put an elephant 9
+"h la/ "t we did ?4 ,2f
+,i "k x1 y'll 2 all gr{n
+up40
+  ,on h} mom's *e/1 ,a2y
 !n put h} h1d &amp; smil$4</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>bottom. "I can't because I'm
-already on the edge. Good heavens,
-you've grown then. When did that
-happen? You could've put an
-elephant in here last time we
-did this. Before I know it, you'll
-be all grown up."
-  On her mom's chest Abby
+          <t xml:space="preserve">  "I can't because I'm already on
+the edge."
+  "Good heavens, you've grown
+then. When did that happen? You
+could've put an elephant in
+here last time we did this. Before
+I know it, you'll be all grown
+up."
+  On her mom's chest, Abby
 then put her head and smiled.</t>
         </is>
       </c>
@@ -6351,10 +6353,10 @@
           <t xml:space="preserve">###   ,! text message sd t
 ,lucy ,josephs 0 a
 failure4 ,x sd %e 0
-ugly1 _h no /yle &amp; ! _w
-hat$ h}4 ,at l1/ t 0 :at
-x sd to ,lucy4 ,x sd t &amp;
-a :ole lot m t %e 0
+ugly1 _h no /yle1 &amp; ! _w
+hat$ h}4 ,at l1/1 t 0
+:at x sd to ,lucy4 ,x sd
+t &amp; a :ole lot m t %e 0
 /ru7l+ to "u/&amp;4 ,!
 actual text ( ! note sd
 t ,lucy bett} n %{ up at
@@ -6367,10 +6369,10 @@
           <t xml:space="preserve">  The text message said that
 Lucy Josephs was a
 failure. It said she was
-ugly, had no style and the world
-hated her. At least that was what
-it said to Lucy. It said that and
-a whole lot more that she was
+ugly, had no style, and the world
+hated her. At least, that was
+what it said to Lucy. It said
+that and a whole lot more that she was
 struggling to understand. The
 actual text of the note said
 that Lucy better not show up at
@@ -6538,8 +6540,8 @@
         <is>
           <t xml:space="preserve">### ph"o 0 / bu7+ h} | l|d z
 %e si&lt;$1 8,i n"e %d h
-giv5 y t ph"o ,lucy40
-  8,no x's f9e1 ,i love
+giv5 y t ph"o1 ,lucy40
+  8,no1 x's f9e1 ,i love
 x10 sd ,lucy "k+ t af=d+
 ! ph"o _h be5 no small
 ?+ = h} "m4
@@ -6554,8 +6556,8 @@
         <is>
           <t xml:space="preserve">phone was still bugging her out loud as
 she sighed, "I never should have
-given you that phone Lucy."
-  "No it's fine, I love
+given you that phone, Lucy."
+  "No, it's fine, I love
 it," said Lucy knowing that affording
 the phone had been no small
 thing for her mother.
@@ -6639,8 +6641,8 @@
 to h} {n 3c}t1 ,lucy
 hesitantly /epp$ | ( !
 c&gt; &amp; walk$ t{&gt;d ! s*ool4
-,x 0 ,jill :o 9 h} f9al
-ye&gt; ( hi&lt; s*ool _h 2come
+,x 0 ,jill :o1 9 h} f9al
+ye&gt; ( hi&lt; s*ool1 _h
 </t>
         </is>
       </c>
@@ -6655,8 +6657,8 @@
 to her own concert, Lucy
 hesitantly stepped out of the
 car and walked toward the school.
-It was Jill who in her final
-year of high school had become
+It was Jill who, in her final
+year of high school, had
 </t>
         </is>
       </c>
@@ -6677,13 +6679,13 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">### 9volv$ 9 help+ organize
-? ye&gt;'s s*ool tal5t %{1
-&amp; %e took h} posi;n v
-s}i|sly4 ,lucy hurri$ 2h
-,jill pull+ on ! worn1
-ov}siz$ coat t _h
-orig9ally 2l;g$ to
+          <t xml:space="preserve">### 2come 9volv$ 9 help+
+organize ? ye&gt;'s s*ool
+tal5t %{1 &amp; %e took h}
+posi;n v s}i|sly4 ,lucy
+hurri$ 2h ,jill pull+ on
+! worn1 ov}siz$ coat t
+_h orig9ally 2l;g$ to
 ,jill1 9 ord} to keep h}
 dry z ! ra9drops fell
 all &gt;.d !m4 ,z ! si/}s
@@ -6693,13 +6695,13 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">involved in helping organize
-this year's school talent show,
-and she took her position very
-seriously. Lucy hurried behind
-Jill pulling on the worn,
-oversized coat that had
-originally belonged to
+          <t xml:space="preserve">become involved in helping
+organize this year's school
+talent show, and she took her
+position very seriously. Lucy
+hurried behind Jill pulling on
+the worn, oversized coat that
+had originally belonged to
 Jill, in order to keep her
 dry as the raindrops fell
 all around them. As the sisters
@@ -6725,7 +6727,7 @@
       <c r="D137" t="inlineStr">
         <is>
           <t xml:space="preserve">### take place1 ,jill fill$
-) excite;t :ile ,lucy
+) excite;t1 :ile ,lucy
 regrett$ t %e _h promis$
 h} "m %e wd "picipate 9
 ! %{4
@@ -6733,15 +6735,15 @@
 2 a r1l %ame1 = y h s* a
 b1uti;l voice10 h} "m _h
 &gt;gu$ two mon?s back :5 !
-3c}t 0 f/ ann|nc$4
-  ,lucy _h be5 3sid}+ x1
+3c}t 0 f/ ann|nc$4 ,lucy
+_h be5 3sid}+ x1 = %e
 </t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
           <t xml:space="preserve">take place, Jill filled
-with excitement while Lucy
+with excitement, while Lucy
 regretted that she had promised
 her mother she would participate in
 the show.
@@ -6749,8 +6751,8 @@
 be a real shame, for you have such a
 beautiful voice," her mother had
 argued two months back when the
-concert was first announced.
-  Lucy had been considering it,
+concert was first announced. Lucy
+had been considering it, for she
 </t>
         </is>
       </c>
@@ -6771,7 +6773,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">### = %e did love to s+4
+          <t xml:space="preserve">### did love to s+4
   ,t v ni&lt;t ! f/ text
 message _h come "?4
   8,h{ does x feel to 2
@@ -6787,7 +6789,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">for she did love to sing.
+          <t xml:space="preserve">did love to sing.
   That very night the first text
 message had come through.
   "How does it feel to be
@@ -6819,32 +6821,32 @@
       <c r="D139" t="inlineStr">
         <is>
           <t xml:space="preserve">### pr|d ( 2+ a ll di6}5t4
-,b text by text1 ,lucy's
-self 3fid;e _h deflat$
+,b text-by-text1 ,lucy's
+self-3fid;e _h deflat$
 &amp;1 9 ! 5d1 x _h tak5 "s
 do+ to get h} to agree
-to p}=m 9 ! %{4 ,n{1
-h{"e1 ,lucy _h no *oice
-b to make h} way t{&gt;ds !
-/age ": ,jill 0 beckon+
-5c|rag+ly to h}4
-  ,%e 0 ! f/ p}=m}4
+to p}=m 9 ! %{4
+  ,n{1 h{"e1 ,lucy _h no
+*oice b to make h} way
+t{&gt;ds ! /age ": ,jill 0
+beckon+ 5c|rag+ly to h}4
+,%e 0 ! f/ p}=m}4
 </t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
           <t xml:space="preserve">proud of being a little different.
-But text by text, Lucy's
-self confidence had deflated
+But text-by-text, Lucy's
+self-confidence had deflated
 and, in the end, it had taken some
 doing to get her to agree
-to perform in the show. Now,
-however, Lucy had no choice
-but to make her way towards the
-stage where Jill was beckoning
-encouragingly to her.
-  She was the first performer.
+to perform in the show.
+  Now, however, Lucy had no
+choice but to make her way
+towards the stage where Jill was
+beckoning encouragingly to her.
+She was the first performer.
 </t>
         </is>
       </c>
@@ -6919,10 +6921,10 @@
 "? ) ? &amp; t %e1 unlike h}
 old} si/}1 0 n 3fid5t 5
 to put h}f 2f ! judg+
-audi;e4 ,! cr{d look$ up
-at h} &amp; ,lucy 0 r1dy to
-run :5 ! f/ notes ( !
-music s.d$ | &amp; a sudd5
+audi;e4
+  ,! cr{d look$ up at h}
+&amp; ,lucy 0 r1dy to run :5
+! f/ notes ( ! music
 </t>
         </is>
       </c>
@@ -6935,10 +6937,10 @@
 through with this and that she, unlike her
 older sister, was not confident enough
 to put herself before the judging
-audience. The crowd looked up
-at her and Lucy was ready to
-run when the first notes of the
-music sounded out and a sudden
+audience.
+  The crowd looked up at her
+and Lucy was ready to run when
+the first notes of the music
 </t>
         </is>
       </c>
@@ -6959,32 +6961,32 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">### calm settl$ ov} h}4 ,%e
-clos$ h} eyes &amp; %ut
-"ey?+ |1 9clud+ !
-audi;e1 ! n}ves t ?r1t5$
-to take ov}1 ! text
-messages1 &amp; ! way !y
-made h} feel4 ,x 0 j h}
-&amp; ! music1 &amp; x 0 a love
-/ory t _h be5 go+ on h}
-:ole life4
+          <t xml:space="preserve">### s.d$ |1 &amp; a sudd5 calm
+settl$ ov} h}4 ,%e clos$
+h} eyes &amp; %ut "ey?+ |1
+9clud+ ! audi;e1 ! n}ves
+t ?r1t5$ to take ov}1 !
+text messages1 &amp; ! way
+!y made h} feel4 ,x 0 j
+h} &amp; ! music1 &amp; x 0 a
+love /ory t _h be5 go+
+on h} :ole life4
   ,%e 2gan to s+1 &amp; all
 </t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">calm settled over her. She
-closed her eyes and shut
-everything out, including the
-audience, the nerves that threatened
-to take over, the text
-messages, and the way they
-made her feel. It was just her
-and the music, and it was a love
-story that had been going on her
-whole life.
+          <t xml:space="preserve">sounded out, and a sudden calm
+settled over her. She closed
+her eyes and shut everything out,
+including the audience, the nerves
+that threatened to take over, the
+text messages, and the way
+they made her feel. It was just
+her and the music, and it was a
+love story that had been going
+on her whole life.
   She began to sing, and all
 </t>
         </is>
@@ -7139,15 +7141,15 @@
         <is>
           <t xml:space="preserve">###   ,! ,roswell ,,ufo
 ,9cid5t 0 ! alleg$
-recov}y (
-extra-t}re/rial debris1
-9clud+ ali5 corpses1 f
-an object t cra%$ ne&gt;
-,roswell1 ,new ,mexico1
-on or ab ,july ei&lt;?1
-n9ete5 =ty-sev54 ,s9ce !
-late n9ete5 sev5ties1 !
-9cid5t has be5 ! subject
+recov}y ( extrat}re/rial
+debris1 9clud+ ali5
+corpses1 f an object t
+cra%$ ne&gt; ,roswell1 ,new
+,mexico1 on or ab ,july
+#h1 #aidg4 ,s9ce ! late
+#aigjs1 ! 9cid5t has be5
+! subject ( 9t5se
+3trov}sy &amp; ! subject (
 </t>
         </is>
       </c>
@@ -7155,15 +7157,15 @@
         <is>
           <t xml:space="preserve">  The Roswell UFO
 Incident was the alleged
-recovery of
-extra-terrestrial debris,
-including alien corpses, from
-an object that crashed near
-Roswell, New Mexico,
-on or about July eighth,
-nineteen forty-seven. Since the
-late nineteen seventies, the
-incident has been the subject
+recovery of extraterrestrial
+debris, including alien
+corpses, from an object that
+crashed near Roswell, New
+Mexico, on or about July
+8, 1947. Since the late
+1970s, the incident has been
+the subject of intense
+controversy and the subject of
 </t>
         </is>
       </c>
@@ -7184,33 +7186,33 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ( 9t5se 3trov}sy &amp; !
-subject ( 3spiracy
-!ories z to ! true
-nature ( ! object t
+          <t xml:space="preserve">### 3spiracy !ories z to !
+true nature ( ! object t
 cra%$4 ,! ,unit$ ,/ates
 milit&gt;y ma9ta9s ! debris
-recov}$ 0 froman
-exp}i;tal hi&lt;-altitude
-surveill.e balloon t
-2l;g$ to a classifi$
-program "nd 8,mogul04
+recov}$ 0 f an exp}i;tal
+hi&lt;-altitude surveill.e
+balloon t 2l;g$ to a
+classifi$ program "nd
+8,mogul40 ,h{"e1 _m
+,,ufo propon5ts ma9ta9
+t1 9 fact1 a cra%$ ali5
 </t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t xml:space="preserve">of intense controversy and the
-subject of conspiracy
-theories as to the true
-nature of the object that
+          <t xml:space="preserve">conspiracy theories as to the
+true nature of the object that
 crashed. The United States
 military maintains the debris
-recovered was froman
-experimental high-altitude
-surveillance balloon that
-belonged to a classified
-program named "Mogul".
+recovered was from an experimental
+high-altitude surveillance
+balloon that belonged to a
+classified program named
+"Mogul." However, many
+UFO proponents maintain
+that, in fact, a crashed alien
 </t>
         </is>
       </c>
@@ -7231,33 +7233,33 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ,h{"e1 _m ,,ufo
-propon5ts ma9ta9 t1 9
-fact1 a cra%$ ali5 craft
-&amp; bodies 7 recov}$1 &amp; t
-! milit&gt;y !n 5gag$ 9 a
-cov}-up4 ,! 9cid5t has
-turn$ 9to a widely "kn
-pop culture ph5om5on1
-mak+ ! "n ,roswell
-synonym|s ) ,,ufo,'s4 ,x
-ranks z "o ( ! mo/
+          <t xml:space="preserve">### craft &amp; bodies 7
+recov}$1 &amp; t ! milit&gt;y
+!n 5gag$ 9 a cov}-up4 ,!
+9cid5t has turn$ 9to a
+widely "kn pop culture
+ph5om5on1 mak+ ! "n
+,roswell synonym|s )
+,,ufo,'s4 ,x ranks z "o
+( ! mo/ publiciz$ &amp;
+3trov}sial alleg$ ,,ufo
+9cid5ts4
 </t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">However, many UFO
-proponents maintain that, in
-fact, a crashed alien craft
-and bodies were recovered, and that
-the military then engaged in a
-cover-up. The incident has
-turned into a widely known
-pop culture phenomenon,
-making the name Roswell
-synonymous with UFOs. It
-ranks as one of the most
+          <t xml:space="preserve">craft and bodies were
+recovered, and that the military
+then engaged in a cover-up. The
+incident has turned into a
+widely known pop culture
+phenomenon, making the name
+Roswell synonymous with
+UFOs. It ranks as one
+of the most publicized and
+controversial alleged UFO
+incidents.
 </t>
         </is>
       </c>
@@ -7278,33 +7280,33 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">### publiciz$ &amp; 3trov}sial
-alleg$ ,,ufo 9cid5ts4
-  ,on ,july n9?1 n9ete5
-=ty-sev51 a press rel1se
-t ,roswell ,&gt;my ,air
-,field issu$ /at$ t
-p}sonnel f ! field's
-,bomb ,gr|p _h recov}$ a
-cra%$ 8fly+ disc0 f a
-ran* ne&gt; ,roswell1 sp&gt;k+
-9t5se m$ia 9t}e/4 ,lat}
+          <t xml:space="preserve">###   ,on ,july #i1 #aidg1 a
+press rel1se t ,roswell
+,&gt;my ,air ,field issu$
+/at$ t p}sonnel f !
+field's ,bomb ,gr|p _h
+recov}$ a cra%$ 8fly+
+disc0 f a ran* ne&gt;
+,roswell1 sp&gt;k+ 9t5se
+m$ia 9t}e/4 ,lat} ! same
+"d1 ! ,comm&amp;+ ,g5}al ( !
+,ei&lt;? ,air ,=ce /at$ t1
 </t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t xml:space="preserve">publicized and controversial
-alleged UFO incidents.
-  On July ninth, nineteen
-forty-seven, a press release
-that Roswell Army Air
-Field issued stated that
-personnel from the field's
-Bomb Group had recovered a
-crashed "flying disc" from a
-ranch near Roswell, sparking
-intense media interest. Later
+          <t xml:space="preserve">  On July 9, 1947, a
+press release that Roswell
+Army Air Field issued
+stated that personnel from the
+field's Bomb Group had
+recovered a crashed "flying
+disc" from a ranch near
+Roswell, sparking intense
+media interest. Later the same
+day, the Commanding General of the
+Eighth Air Force stated that,
 </t>
         </is>
       </c>
@@ -7325,33 +7327,33 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ! same "d1 ! ,comm&amp;+
-,g5}al ( ! ,ei&lt;? ,air
-,=ce /at$ t1 9 fact1 a
-w1!r balloon _h be5
-recov}$ by ! ,roswell
-,&gt;my ,air ,field
-p}sonnel1 r ?an a 8fly+
-sauc}40 ,a subsequ5t
-press 3f};e 0 call$1
-f1tur+ debris f ! cra%$
-object t 3firm$ ! w1!r
+          <t xml:space="preserve">### 9 fact1 a w1!r balloon
+_h be5 recov}$ by !
+,roswell ,&gt;my ,air
+,field p}sonnel1 r ?an a
+8fly+ sauc}40 ,a
+subsequ5t press 3f};e 0
+call$1 f1tur+ debris f !
+cra%$ object t 3firm$ !
+w1!r balloon descrip;n4
+,! case 0 qkly =gott5 &amp;
+alm completely ignor$1
 </t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">the same day, the Commanding
-General of the Eighth Air
-Force stated that, in fact, a
-weather balloon had been
-recovered by the Roswell
-Army Air Field
-personnel, rather than a "flying
-saucer." A subsequent
-press conference was called,
-featuring debris from the crashed
-object that confirmed the weather
+          <t xml:space="preserve">in fact, a weather balloon
+had been recovered by the
+Roswell Army Air
+Field personnel, rather than a
+"flying saucer." A
+subsequent press conference was
+called, featuring debris from the
+crashed object that confirmed the
+weather balloon description.
+The case was quickly forgotten and
+almost completely ignored,
 </t>
         </is>
       </c>
@@ -7372,33 +7374,33 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">### balloon descrip;n4 ,!
-case 0 qkly =gott5 &amp; alm
-completely ignor$1 ev5
-by ,,ufo rese&gt;*}s1 = m
-?an ?irty ye&gt;s4 ,!n;19
-n9ete5 sev5ty-ei&lt;t1
-nucle&gt; physici/ &amp; au?or
-,/anton ,fri$man
-9t}view$ ,jesse ,m&gt;cel1
-! only p}son "kn to h
-a3ompani$ ! ,roswell
+          <t xml:space="preserve">### ev5 by ,,ufo rese&gt;*}s1 =
+m ?an ?irty ye&gt;s4
+  ,!n1 9 #aigh1 nucle&gt;
+physici/ &amp; au?or ,/anton
+,fri$man 9t}view$ ,jesse
+,m&gt;cel1 ! only p}son "kn
+to h a3ompani$ !
+,roswell debris f ": x 0
+recov}$ to ,=t ,wor?4
+,ov} ! next few ye&gt;s1 !
+a3.ts he &amp; o!rs gave
 </t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">balloon description. The
-case was quickly forgotten and almost
-completely ignored, even
-by UFO researchers, for more
-than thirty years. Then;1in
-nineteen seventy-eight,
-nuclear physicist and author
-Stanton Friedman
-interviewed Jesse Marcel,
-the only person known to have
-accompanied the Roswell
+          <t xml:space="preserve">even by UFO researchers, for
+more than thirty years.
+  Then, in 1978, nuclear
+physicist and author Stanton
+Friedman interviewed Jesse
+Marcel, the only person known
+to have accompanied the
+Roswell debris from where it was
+recovered to Fort Worth.
+Over the next few years, the
+accounts he and others gave
 </t>
         </is>
       </c>
@@ -7419,33 +7421,33 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">### debris f ": x 0 recov}$
-to ,=t ,wor?4 ,ov} !
-next few ye&gt;s1 ! a3.t %e
-&amp; o!rs gave elevat$
-,roswell f a =gott5
-9cid5t to p}h ! mo/
-fam|s ,,ufo case ( all
-"t4
-  ,by ! e&gt;ly n9ete5
-n9eties1 ,,ufo rese&gt;*}s
-_h 9t}view$ s"eal hundr$
+          <t xml:space="preserve">### elevat$ ,roswell f a
+=gott5 9cid5t to p}h !
+mo/ fam|s ,,ufo case (
+all "t4
+  ,by ! e&gt;ly #aiijs1
+,,ufo rese&gt;*}s _h
+9t}view$ s"eal hundr$ p
+:o _h1 or :o claim$ to h
+_h1 a 3nec;n ) ! ev5ts
+at ,roswell 9 #aidg4
+,addi;nally1 hundr$s (
 </t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">debris from where it was recovered
-to Fort Worth. Over the
-next few years, the account she
-and others gave elevated
-Roswell from a forgotten
-incident to perhaps the most
-famous UFO case of all
-time.
-  By the early nineteen
-nineties, UFO researchers
-had interviewed several hundred
+          <t xml:space="preserve">elevated Roswell from a
+forgotten incident to perhaps the
+most famous UFO case of
+all time.
+  By the early 1990s,
+UFO researchers had
+interviewed several hundred people
+who had, or who claimed to have
+had, a connection with the events
+at Roswell in 1947.
+Additionally, hundreds of
 </t>
         </is>
       </c>
@@ -7466,33 +7468,33 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">### p :o _h1 or :o claim$ to
-h _h1 a 3nec;n ) ! ev5ts
-at ,roswell 9 n9ete5
-=ty-sev54 ,addi;nally1
-hundr$s ( docu;ts 7
-obta9$ by ,fre$om (
-,9=ma;n ,act reque/s1 z
-7 "s t 9sid}s app&gt;5tly
-l1k$4 ,_! 3clu.ns 7 t at
-l1/ "o ali5 craft _h
-cra%$ 9 ! ,roswell
+          <t xml:space="preserve">### docu;ts 7 obta9$ by
+,fre$om ( ,9=ma;n ,act
+reque/s1 z 7 "s t 9sid}s
+app&gt;5tly l1k$4 ,_!
+3clu.ns 7 t at l1/ "o
+ali5 craft _h cra%$ 9 !
+,roswell vic9;y1 t
+ali5s1 "s possibly /
+alive1 7 recov}$1 &amp; t a
+massive cov}-up ( any k
+( ! 9cid5t 0 put 9
 </t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t xml:space="preserve">people who had, or who claimed to
-have had, a connection with the events
-at Roswell in nineteen
-forty-seven. Additionally,
-hundreds of documents were
-obtained by Freedom of
-Information Act requests, as
-were some that insiders apparently
-leaked. Their conclusions were that at
-least one alien craft had
-crashed in the Roswell
+          <t xml:space="preserve">documents were obtained by
+Freedom of Information Act
+requests, as were some that insiders
+apparently leaked. Their
+conclusions were that at least one
+alien craft had crashed in the
+Roswell vicinity, that
+aliens, some possibly still
+alive, were recovered, and that a
+massive cover-up of any knowledge
+of the incident was put in
 </t>
         </is>
       </c>
@@ -7513,33 +7515,33 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">### vic9;y1 t ali5s1 "s
-possibly / alive1 7
-recov}$1 &amp; t a massive
-cov}-up ( any k ( !
-9cid5t 0 put 9 place4
+          <t xml:space="preserve">### place4
   ,num}|s books1
 &gt;ticles1 televi.n
-specials &amp; ev5 a
+specials1 &amp; ev5 a
 made-=-,,tv movie br"| !
-n9ete5 =ty-sev5 9cid5t
-fame &amp; notoriety s t by
+#aidg 9cid5t fame &amp;
+notoriety s t by !
+mid-#aiijs1 /r;g
+majorities 9 polls1 s* z
+a #aiig ,,cnn_/,"t poll1
+2liev$ t ali5s _h visit$
 </t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicinity, that aliens, some
-possibly still alive, were
-recovered, and that a massive
-cover-up of any knowledge of the
-incident was put in place.
+          <t xml:space="preserve">place.
   Numerous books,
 articles, television
-specials and even a
+specials, and even a
 made-for-TV movie brought the
-nineteen forty-seven incident
-fame and notoriety so that by
+1947 incident fame and
+notoriety so that by the
+mid-1990s, strong
+majorities in polls, such as
+a 1997 CNN/Time poll,
+believed that aliens had visited
 </t>
         </is>
       </c>
@@ -7560,33 +7562,33 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ! mid n9ete5 n9eties1
-/r;g majorities 9 polls1
-s* z a n9ete5 n9ety sev5
-,,cnn_/,"t poll1 2liev$
-t ali5s _h visit$ e&gt;? &amp;
-specifically t ali5s _h
-l&amp;$ at ,roswell &amp; !
-gov}n;t 0 cov}+ up !
+          <t xml:space="preserve">### e&gt;? &amp; specifically t
+ali5s _h l&amp;$ at ,roswell
+&amp; ! gov}n;t 0 cov}+ up !
 fact4
-  ,dur+ ! n9ete5 ei&lt;ties
-&amp; n9ete5 n9eties1 a new
+  ,dur+ ! #aihjs &amp;
+#aiijs1 a new n&gt;rative
+em}g$ : 0 at /r;g odds )
+:at 0 report$ 9 #aidg4
+,? n&gt;rative evolv$ ov} !
+ye&gt;s f ! "t ! f/ book on
+,roswell 0 publi%$ 9
 </t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">the mid nineteen nineties,
-strong majorities in polls,
-such as a nineteen ninety seven
-CNN/Time poll, believed
-that aliens had visited earth and
-specifically that aliens had
-landed at Roswell and the
-government was covering up the
+          <t xml:space="preserve">earth and specifically that
+aliens had landed at Roswell
+and the government was covering up the
 fact.
-  During the nineteen eighties
-and nineteen nineties, a new
+  During the 1980s and
+1990s, a new narrative
+emerged which was at strong odds with
+what was reported in 1947.
+This narrative evolved over the
+years from the time the first book on
+Roswell was published in
 </t>
         </is>
       </c>
@@ -7607,33 +7609,33 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">### n&gt;rative em}g$ : 0 at
-/r;g odds ) :at 0
-report$ 9 n9ete5 =ty
-sev54 ,? n&gt;rative evolv$
-ov} ! ye&gt;s f ! "t ! f/
-book on ,roswell 0
-publi%$ 9 n9ete5 ei&lt;t z
-_m new wit;ses &amp; a3.ts
-em}g$1 drawn | 9 "p by !
-public;y on ! 9cid5t4 ,(
-! hundr$s ( wit;ses t !
+          <t xml:space="preserve">### #aihj z _m new wit;ses &amp;
+a3.ts em}g$1 drawn | 9
+"p by ! public;y on !
+9cid5t4
+  ,( ! hundr$s ( wit;ses
+t ! v&gt;i|s rese&gt;*}s
+9t}view$ - a seem+ly
+impressive figure - a
+comp&gt;able few 7 true
+8wit;ses0 :o claim$ to h
+actually se5 debris or
 </t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">narrative emerged which was at
-strong odds with what was
-reported in nineteen forty
-seven. This narrative evolved
-over the years from the time the first
-book on Roswell was
-published in nineteen eight as
-many new witnesses and accounts
-emerged, drawn out in part by the
-publicity on the incident. Of
-the hundreds of witnesses that the
+          <t xml:space="preserve">1980 as many new witnesses and
+accounts emerged, drawn out in
+part by the publicity on the
+incident.
+  Of the hundreds of witnesses
+that the various researchers
+interviewed - a seemingly
+impressive figure - a
+comparable few were true
+"witnesses" who claimed to have
+actually seen debris or
 </t>
         </is>
       </c>
@@ -7654,80 +7656,80 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">### v&gt;i|s rese&gt;*}s 9t}view$
-- a seem+ly impressive
-figure - a comp&gt;able few
-7 true 8wit;ses0 :o
-claim$ to h actually se5
-debris or ali5s4 ,mo/ (
-~! s-call$ wit;ses 7
-rep1t+ ! claims ( o!rs1
-&amp; _! te/imony wd 2
+          <t xml:space="preserve">### ali5s4 ,mo/ ( ~! s-call$
+wit;ses 7 rep1t+ !
+claims ( o!rs1 &amp; _!
+te/imony wd 2
 9admissible he&gt;say 9 an
 ,am}ican c|rt4 ,z = !
-</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">various researchers interviewed
-- a seemingly impressive
-figure - a comparable few
-were true "witnesses" who
-claimed to have actually seen
-debris or aliens. Most of
-these so-called witnesses were
-repeating the claims of others,
-and their testimony would be
-inadmissible hearsay in an
-American court. As for the
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>13</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>08-13</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### s"eal a3.ts f ~? :o
+s"eal a3.ts f ~? :o
 claim$ to h se5 ali5s1
 critics id5tifi$ a
 v&gt;iety ( problems ) !m4
 ,~! problems rang$ f !
-reliabil;y ( second-h&amp;
+</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aliens. Most of these so-called
+witnesses were repeating the
+claims of others, and their
+testimony would be
+inadmissible hearsay in an
+American court. As for the
+several accounts from those who
+claimed to have seen aliens,
+critics identified a
+variety of problems with them.
+These problems ranged from the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>13</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>08-13</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### reliabil;y ( second-h&amp;
 a3.ts1 to s}i|s
 cr$ibil;y problems )
 wit;ses mak+ demon/rably
 false or 9t}nally
 9consi/5t claims1 to
+dubi|s d1?b$ 83fes.ns0
+or a3.ts f eld}ly or
+easily 3fus$ wit;ses4 ,a
+basic problem ) all !
+wit;s a3.ts1 ac to !
 </t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">several accounts from those who
-claimed to have seen aliens,
-critics identified a
-variety of problems with them.
-These problems ranged from the
-reliability of second-hand
+          <t xml:space="preserve">reliability of second-hand
 accounts, to serious
 credibility problems with
 witnesses making demonstrably
 false or internally
 inconsistent claims, to
+dubious deathbed "confessions"
+or accounts from elderly or
+easily confused witnesses. A
+basic problem with all the
+witness accounts, according to the
 </t>
         </is>
       </c>
@@ -7748,127 +7750,127 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">### dubi|s d1?-b$ 83fes.ns0
-or a3.ts f eld}ly or
-easily 3fus$ wit;ses4 ,a
-basic problem ) all !
-wit;s a3.ts1 ac to !
-critics1 is t !y all
+          <t xml:space="preserve">### critics1 is t !y all
 came a m9imum ( ?irty-"o
 ye&gt;s af ! ev5ts 9 "q1 &amp;
 9 _m cases 7 rec.t$ m
 ?an =ty ye&gt;s af ! fact4
 ,n only &gt;e memories ?
+old ( dubi|s reliabil;y1
+!y 7 al subject to
+3tam9a;n f o!r a3.ts !
+wit;ses may h be5 expos$
+to4
 </t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">dubious death-bed "confessions"
-or accounts from elderly or
-easily confused witnesses. A
-basic problem with all the
-witness accounts, according to the
-critics, is that they all
+          <t xml:space="preserve">critics, is that they all
 came a minimum of thirty-one
 years after the events in question, and
 in many cases were recounted more
 than forty years after the fact.
 Not only are memories this
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>15</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>08-15</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### old ( dubi|s reliabil;y1
-!y 7 al subject to
-3tam9a;n f o!r a3.ts !
-wit;ses may h be5 expos$
-to4
-  ,?|&lt; "! _h alw be5
-skeptics :o _h _m
-objec;ns to !
-plausibil;y ( ~! a3.ts1
-x 0 n until ! mid n9ete5
-n9eties t a /r;g
-</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">old of dubious reliability,
+old of dubious reliability,
 they were also subject to
 contamination from other accounts the
 witnesses may have been exposed
 to.
-  Though there had always been
-skeptics who had many
-objections to the
-plausibility of these accounts,
-it was not until the mid nineteen
-nineties that a strong
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B161" t="n">
-        <v>16</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>08-16</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### c.t}-&gt;gu;t to ! pres;e (
-ali5s 0 widely
+      <c r="B160" t="n">
+        <v>15</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>08-15</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">###   ,?|&lt; "! _h alw be5
+skeptics :o _h _m
+objec;ns to !
+plausibil;y ( ~! a3.ts1
+x 0 n until ! mid-#aiijs
+t a /r;g c.t}-&gt;gu;t to !
+pres;e ( ali5s 0 widely
 publiciz$4 ,! ,g5}al
 ,a3.t+ ,(fice laun*$ an
 9quiry &amp; direct$ !
 ,(fice ( ! ,secret&gt;y ( !
-,air ,=ce to 3duct an
-9t}nal 9ve/iga;n4 ,!
-result 0 summ&gt;iz$ 9 two
-reports4 ,! f/1 rel1s$ 9
-n9ete5 n9ety-five1
-</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">counter-argument to the presence of
-aliens was widely
+</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Though there had always been
+skeptics who had many
+objections to the
+plausibility of these accounts,
+it was not until the mid-1990s
+that a strong counter-argument to the
+presence of aliens was widely
 publicized. The General
 Accounting Office launched an
 inquiry and directed the
 Office of the Secretary of the
-Air Force to conduct an
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>16</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>08-16</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### ,air ,=ce to 3duct an
+9t}nal 9ve/iga;n4 ,!
+result 0 summ&gt;iz$ 9 two
+reports4 ,! f/1 rel1s$ 9
+#aiie1 3clud$ t !
+report$ recov}$ mat}ial
+9 #aidg 0 likely debris
+f a secret gov}n;t
+program call$ ,project
+,mogul1 : 9volv$
+hi&lt;-altitude balloons
+</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Air Force to conduct an
 internal investigation. The
 result was summarized in two
 reports. The first, released in
-nineteen ninety-five,
+1995, concluded that the
+reported recovered material
+in 1947 was likely debris
+from a secret government
+program called Project
+Mogul, which involved
+high-altitude balloons
 </t>
         </is>
       </c>
@@ -7889,33 +7891,33 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">### 3clud$ t ! report$
-recov}$ mat}ial 9 n9ete5
-=ty-sev5 0 likely debris
-f a secret gov}n;t
-program call$ ,project
-,mogul1 : 9volv$ hi&lt;
-altitude balloons m1nt
-to detect s.d waves
+          <t xml:space="preserve">### m1nt to detect s.d waves
 g5}at$ by ,soviet atomic
 bomb te/s &amp; balli/ic
-missiles4 ,! second
+missiles4
+  ,! second report1
+rel1s$ two ye&gt;s lat}1 9
+#aiig1 3clud$ t reports
+( recov}$ ali5 bodies 7
+likely a comb9a;n (3
+9noc5tly trans=m$
+memories ( milit&gt;y
 </t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">concluded that the reported
-recovered material in nineteen
-forty-seven was likely debris
-from a secret government
-program called Project
-Mogul, which involved high
-altitude balloons meant
-to detect sound waves
+          <t xml:space="preserve">meant to detect sound waves
 generated by Soviet atomic
 bomb tests and ballistic
-missiles. The second
+missiles.
+  The second report,
+released two years later, in
+1997, concluded that reports
+of recovered alien bodies were
+likely a combination of:
+innocently transformed
+memories of military
 </t>
         </is>
       </c>
@@ -7936,127 +7938,127 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">### report1 rel1s$ two ye&gt;s
-lat}1 9 n9ete5
-n9ety-sev51 3clud$ t
-reports ( recov}$ ali5
-bodies 7 likely a
-comb9a;n (3 9noc5tly
-trans=m$ memories (
-milit&gt;y a3id5ts 9volv+
-9jur$ or kill$ p}sonnel2
-9noc5tly trans=m$
-memories ( ! recov}y (
-</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">report, released two years
-later, in nineteen
-ninety-seven, concluded that
-reports of recovered alien
-bodies were likely a
-combination of: innocently
-transformed memories of
-military accidents involving
-injured or killed personnel;
-innocently transformed
-memories of the recovery of
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>19</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>08-19</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### an?ropomorphic dummies 9
-milit&gt;y programs ,,u
-3duct$ 9 ! n9ete5
-fifties2 &amp; hoaxes t
-v&gt;i|s wit;ses &amp; ,,ufo
+          <t xml:space="preserve">### a3id5ts 9volv+ 9jur$ or
+kill$ p}sonnel2 9noc5tly
+trans=m$ memories ( !
+recov}y ( an?ropomorphic
+dummies 9 milit&gt;y
+programs ,,u 3duct$ 9 !
+#aiejs2 &amp; hoaxes t v&gt;i|s
+wit;ses &amp; ,,ufo
 propon5ts p}petrat$4 ,!
 psy*ological e6ects ( "t
 compres.n &amp; 3fu.n ab :5
-ev5ts o3urr$ expla9$ !
-4crepancy ) ! ye&gt;s 9 "q4
-  ,9 ,janu&gt;y n9ete5
-</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">anthropomorphic dummies in
-military programs US
-conducted in the nineteen
-fifties; and hoaxes that
-various witnesses and UFO
+</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">accidents involving injured or
+killed personnel; innocently
+transformed memories of the
+recovery of anthropomorphic
+dummies in military
+programs US conducted in the
+1950s; and hoaxes that various
+witnesses and UFO
 proponents perpetrated. The
 psychological effects of time
 compression and confusion about when
-events occurred explained the
-discrepancy with the years in question.
-  In January nineteen
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B165" t="n">
-        <v>20</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>08-20</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### n9ety-sev51 ,k&gt;l
+      <c r="B164" t="n">
+        <v>19</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>08-19</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### ev5ts o3urr$ expla9$ !
+4crepancy ) ! ye&gt;s 9 "q4
+  ,9 ,janu&gt;y #aiig1 ,k&gt;l
 ,pflock1 "o ( ! m
 prom95t pro-,,ufo
 rese&gt;*}s1 sd3 8,bas$ on
 my rese&gt;* &amp; t ( o!rs1
 ,i'm z c}ta9 z x's
 possible to 2 )|t
-absolute pro(1 t no fly+
+absolute pro( t no fly+
 sauc} or sauc}s cra%$ 9
-! g5}al vic9;y (
-,roswell or on ! ,pla9s
-</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ninety-seven, Karl
+</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">events occurred explained the
+discrepancy with the years in question.
+  In January 1997, Karl
 Pflock, one of the more
 prominent pro-UFO
 researchers, said: "Based on
 my research and that of others,
 I'm as certain as it's
 possible to be without
-absolute proof, that no flying
+absolute proof that no flying
 saucer or saucers crashed in
-the general vicinity of
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>20</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>08-20</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### ! g5}al vic9;y (
+,roswell or on ! ,pla9s
+( ,san ,agu/9 9 #aidg4,7
+,he !n add$3 8,! debris
+f.d 0 ! rema9s ( "s?+ v
+e&gt;?ly1 all b c}ta9ly
+"s?+ f ! ,top ,secret
+,project ,mogul40
+  ,al? mo/ n{ agree ) ?
+3clu.n1 ea* ye&gt;1 dur+
+,july ,f|r? week5d1 !
+</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the general vicinity of
 Roswell or on the Plains
+of San Agustin in 1947.[
+He then added: "The debris
+found was the remains of something very
+earthly, all but certainly
+something from the Top Secret
+Project Mogul."
+  Although most now agree with this
+conclusion, each year, during
+July Fourth weekend, the
 </t>
         </is>
       </c>
@@ -8077,83 +8079,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">### ( ,san ,agu/9 9 n9ete5
-=ty-sev540 ,he !n add$3
-8,! debris f.d 0 !
-rema9s ( "s?+ v e&gt;?ly1
-all b c}ta9ly "s?+ f !
-,top ,secret ,project
-,mogul40
-  ,al? mo/ n{ agree ) ?
-3clu.n1 ea* ye&gt;1 dur+
-,july ,f|r? ,week5d1 !
-,c;y ( ,roswell ho/s !
-</t>
+          <t>### ,c;y ( ,roswell ho/s !
+,roswell ,,ufo ,fe/ival
+celebrat+ all ?+s ,,ufo1
+f1tur+ prom95t
+,,ufo,'logi/s &amp; 4cus.ns4</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">of San Agustin in nineteen
-forty-seven." He then added:
-"The debris found was the
-remains of something very earthly,
-all but certainly something from the
-Top Secret Project
-Mogul."
-  Although most now agree with this
-conclusion, each year, during
-July Fourth Weekend, the
-City of Roswell hosts the
-</t>
+          <t>City of Roswell hosts the
+Roswell UFO Festival
+celebrating all things UFO,
+featuring prominent
+UFOlogists and discussions.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>09</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>08-22</t>
+          <t>09-01</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
-        <is>
-          <t>### ,roswell ,,ufo ,fe/ival
-celebrat+ all ?+s ,,ufo
-f1tur+ prom95t
-,,ufo,'logi/s &amp; 4cus.ns4</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Roswell UFO Festival
-celebrating all things UFO
-featuring prominent
-UFOlogists and discussions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>1</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>09-01</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
         <is>
           <t xml:space="preserve">###   ,tulip mania 0 a p}iod
 9 ! ,dut* ,gold5 ,age
@@ -8163,13 +8120,13 @@
 extraord9&gt;ily hi&lt; levels
 &amp; !n sudd5ly collaps$4
 ,at ! p1k ( tulip mania
-9 ,febru&gt;y sixte5
-?irty-sev51 tulip
+9 ,febru&gt;y #afcg1 tulip
 3tracts sold = m ?an t5
-</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
+"ts ! annual 9come ( a
+</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
         <is>
           <t xml:space="preserve">  Tulip mania was a period
 in the Dutch Golden Age
@@ -8179,126 +8136,124 @@
 extraordinarily high levels
 and then suddenly collapsed.
 At the peak of tulip mania
-in February sixteen
-thirty-seven, tulip
+in February 1637, tulip
 contracts sold for more than ten
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+times the annual income of a
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B169" t="n">
+      <c r="B168" t="n">
         <v>2</v>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>09-02</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### "ts ! annual 9come ( a
-skill$ craftsman4 ,x is
+      <c r="D168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### skill$ craftsman4 ,x is
 g5}ally 3sid}$ ! f/
 record$ economic bu2le4
   ,! tulip1 9troduc$ to
-,europe 9 ! mid sixte5?
+,europe 9 ! mid-sixte5?
 c5tury f ! ,ottoman
 ,empire1 2came v popul&gt;
 9 ! ,unit$ ,prov9ces1 :
 we n{ "k z ! ,ne!rl&amp;s4
 ,tulip cultiva;n 9 !
-</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">times the annual income of a
-skilled craftsman. It is
+,unit$ ,prov9ces is
+</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">skilled craftsman. It is
 generally considered the first
 recorded economic bubble.
   The tulip, introduced to
-Europe in the mid sixteenth
+Europe in the mid-sixteenth
 century from the Ottoman
 Empire, became very popular
 in the United Provinces, which
 we now know as the Netherlands.
 Tulip cultivation in the
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+United Provinces is
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B170" t="n">
+      <c r="B169" t="n">
         <v>3</v>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>09-03</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### ,unit$ ,prov9ces is
-g5}ally ?"| to h /&gt;t$ 9
-e&gt;ne/ &gt;.d fifte5
-n9ety-?ree af ! ,flemi%
-botani/ ,*&gt;les de
-l',~/ecluse _h tak5 up a
-po/ at ! ,univ}s;y (
-,leid5 &amp; e/abli%$ a
+      <c r="D169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### g5}ally ?"| to h /&gt;t$ 9
+e&gt;ne/ &gt;.d #aeic af !
+,flemi% botani/ ,*&gt;les
+de l',~/ecluse _h tak5
+up a po/ at ! ,univ}s;y
+( ,leid5 &amp; e/abli%$ a
 botanical g&gt;d51 : is
 fam|s z "o ( ! olde/ 9 !
 _w4 ,"!1 he plant$ 8
-</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">United Provinces is
-generally thought to have started in
-earnest around fifteen
-ninety-three after the Flemish
-botanist Charles de
-l'~stecluse had taken up a
-post at the University of
-Leiden and established a
+collec;n ( tulip bulbs t
+! ,emp}or's ambassador
+</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">generally thought to have started in
+earnest around 1593 after the
+Flemish botanist Charles
+de l'~stecluse had taken
+up a post at the University
+of Leiden and established a
 botanical garden, which is
 famous as one of the oldest in the
 world. There, he planted his
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+collection of tulip bulbs that
+the Emperor's ambassador
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B171" t="n">
+      <c r="B170" t="n">
         <v>4</v>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C170" t="inlineStr">
         <is>
           <t>09-04</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### collec;n ( tulip bulbs1
-t ! ,emp}or's ambassador
-s5t to hm f ,turkey1 : 7
+      <c r="D170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### s5t to hm f ,turkey1 : 7
 able to tol}ate ! h&gt;%}
 3di;ns ( ! nor!rn
 climate4 ,x 0 %ortly
@@ -8307,14 +8262,14 @@
   ,! fl{} rapidly 2came
 a covet$ luxury item &amp; a
 /atus symbol1 &amp; a pr(u.n
-</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">collection of tulip bulbs,
-that the Emperor's ambassador
-sent to him from Turkey, which were
+( v&gt;ieties foll{$4 ,!y 7
+classifi$ 9 gr|ps3
+</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sent to him from Turkey, which were
 able to tolerate the harsher
 conditions of the northern
 climate. It was shortly
@@ -8323,29 +8278,29 @@
   The flower rapidly became
 a coveted luxury item and a
 status symbol, and a profusion
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+of varieties followed. They were
+classified in groups:
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B172" t="n">
+      <c r="B171" t="n">
         <v>5</v>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>09-05</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### ( v&gt;ieties foll{$4 ,!y 7
-classifi$ 9 gr|ps3
-"o-color$ tulips ( r$1
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### "o-color$ tulips ( r$1
 yell{1 or :ite 7 "kn z
 ,c|l}51 b x 0 !
 multicolor$ ,ros5 "&lt;r$
@@ -8354,14 +8309,14 @@
 "&lt;purple or lilac on
 :ite backgr.d"&gt;1 &amp;1 to a
 less} ext5t1 ! ,biz&gt;d5
-</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">of varieties followed. They were
-classified in groups:
-one-colored tulips of red,
+"&lt;r$1 br{n1 or purple on
+yell{ backgr.d"&gt; t 7 !
+</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one-colored tulips of red,
 yellow, or white were known as
 Couleren, but it was the
 multicolored Rosen "ghred
@@ -8370,217 +8325,217 @@
 "ghpurple or lilac on
 white background"ar, and, to a
 lesser extent, the Bizarden
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+"ghred, brown, or purple on
+yellow background"ar that were the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B173" t="n">
+      <c r="B172" t="n">
         <v>6</v>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>09-06</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### "&lt;r$1 br{n or purple on
-yell{ backgr.d"&gt; t 7 !
-mo/ popul&gt;4 ,~!
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### mo/ popul&gt;4 ,~!
 spectacul&gt; &amp; hi&lt;ly
 s"|-af tulip bulbs wd
 gr{ fl{}s ) vivid
 colors1 l9es1 &amp; flames
-on ! petals1 z a result1
-x is n{ "u/ood1 ( 2+
-9fect$ ) tulip-specific
-virus "kn z ! 8,tulip
-</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"ghred, brown or purple on
-yellow background"ar that were the
-most popular. These
+on ! petals - z a
+result1 x is n{ "u/ood1
+( 2+ 9fect$ )
+tulip-specific virus "kn
+z ! tulip br1k+ virus4
+  ,! ,dut* ,gold5 ,age
+</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">most popular. These
 spectacular and highly
 sought-after tulip bulbs would
 grow flowers with vivid
 colors, lines, and flames
-on the petals, as a result,
-it is now understood, of being
-infected with tulip-specific
-virus known as the "Tulip
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+on the petals - as a
+result, it is now understood,
+of being infected with
+tulip-specific virus known
+as the tulip breaking virus.
+  The Dutch Golden Age
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B174" t="n">
+      <c r="B173" t="n">
         <v>7</v>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>09-07</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### br1k+ virus04
-  ,! ,dut* ,gold5 ,age
-gr{}s "nd _! new
+      <c r="D173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### gr{}s "nd _! new
 v&gt;ieties ) exalt$
 titles4 ,_m e&gt;ly =ms 7
-prefix$ ) 8admiral01 (t5
+prefix$ ) 8admiral10 (t5
 comb9$ ) ! gr{}s' "ns4
 8,g5}al0 0 ano!r prefix
 t f.d xs way 9to ! "ns (
 &gt;.d ?irty v&gt;ieties4
 ,lat} came v&gt;ieties )
-</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">breaking virus".
-  The Dutch Golden Age
-growers named their new
+ev5 m sup}b "ns1 s* z
+ev5 8,admiral (
+</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">growers named their new
 varieties with exalted
 titles. Many early forms were
-prefixed with "admiral", often
+prefixed with "admiral," often
 combined with the growers' names.
 "General" was another prefix
 that found its way into the names of
 around thirty varieties.
 Later came varieties with
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+even more superb names, such as
+even "Admiral of
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B175" t="n">
+      <c r="B174" t="n">
         <v>8</v>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>09-08</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### ev5 m sup}b "ns1 s* z
-ev5 8,admiral (
-,admirals0 &amp; 8,g5}al (
-,g5}als04 ,mo/ ( ~!
+      <c r="D174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### ,admirals0 &amp; 8,g5}al (
+,g5}als40 ,mo/ ( ~!
 v&gt;ieties h n{ di$ |1 ?|&lt;
 simil&gt; 8brok50 tulips
 3t9ue 9 ! trade4
-  ,tulips gr{ f bulbs1 &amp;
+  ,tulips gr{ f bulbs &amp;
 c 2 propagat$ "? bo?
 se$s &amp; buds4 ,se$s f a
 tulip w =m a fl{}+ bulb
-</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">even more superb names, such as
-even "Admiral of
-Admirals" and "General of
-Generals". Most of these
+af #g-#ab ye&gt;s4 ,:5 a
+bulb gr{s 9to ! fl{}1 !
+</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admirals" and "General of
+Generals." Most of these
 varieties have now died out, though
 similar "broken" tulips
 continue in the trade.
-  Tulips grow from bulbs, and
+  Tulips grow from bulbs and
 can be propagated through both
 seeds and buds. Seeds from a
 tulip will form a flowering bulb
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+after 7-12 years. When a
+bulb grows into the flower, the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B176" t="n">
+      <c r="B175" t="n">
         <v>9</v>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>09-09</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### af sev5-twelve ye&gt;s4 ,:5
-a bulb gr{s 9to ! fl{}1
-! orig9al bulb w 4appe&gt;1
-b a cl"o bulb =ms 9 xs
+      <c r="D175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### orig9al bulb w 4appe&gt;1 b
+a cl"o bulb =ms 9 xs
 place1 z d s"eal buds4
 ,prop}ly cultivat$1 ~!
 buds w 2come bulbs ( _!
-{n4 ,! 8tulip br1k+0
+{n4 ,! tulip br1k+
 virus1 : _m botani/s h
 /udi$1 spr1ds only "?
 buds1 n se$s1 &amp; s
-</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">after seven-twelve years. When
-a bulb grows into the flower,
-the original bulb will disappear,
-but a clone bulb forms in its
+cultivat+ ! mo/ app1l+
+v&gt;ieties takes ye&gt;s4
+</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">original bulb will disappear, but
+a clone bulb forms in its
 place, as do several buds.
 Properly cultivated, these
 buds will become bulbs of their
-own. The "tulip breaking"
+own. The tulip breaking
 virus, which many botanists have
 studied, spreads only through
 buds, not seeds, and so
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+cultivating the most appealing
+varieties takes years.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B177" t="n">
+      <c r="B176" t="n">
         <v>10</v>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>09-10</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### cultivat+ ! mo/ app1l+
-v&gt;ieties takes ye&gt;s4
-,propaga;n is grtly sl{$
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### ,propaga;n is grtly sl{$
 d{n by ! virus4 ,tulips
 bloom 9 ,april &amp; ,may =
 ab a week1 &amp; ! second&gt;y
@@ -8589,14 +8544,14 @@
 mov$ ab f ,june to
 ,septemb}1 &amp; ?us actual
 pur*ases o3urr$ dur+ ~!
-</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cultivating the most appealing
-varieties takes years.
-Propagation is greatly slowed
+mon?s4
+  ,z ! fl{}s grew 9
+</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Propagation is greatly slowed
 down by the virus. Tulips
 bloom in April and May for
 about a week, and the secondary
@@ -8605,6 +8560,55 @@
 moved about from June to
 September, and thus actual
 purchases occurred during these
+months.
+  As the flowers grew in
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>11</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>09-11</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### popul&gt;;y1 pr(es.nal
+gr{}s pd hi&lt;} &amp; hi&lt;}
+prices = bulbs ) !
+virus4 ,by #afcd1 9 "p z
+a result ( dem&amp; f !
+,fr5*1 speculators 2gan
+to 5t} ! m&gt;ket4 ,9
+#afcf1 ! ,dut* cr1t$ a
+type ( =mal futures
+m&gt;kets : m}*ants us$ to
+sell &amp; buy 3tracts to
+</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">popularity, professional
+growers paid higher and higher
+prices for bulbs with the
+virus. By 1634, in part as
+a result of demand from the
+French, speculators began
+to enter the market. In
+1636, the Dutch created a
+type of formal futures
+markets which merchants used to
+sell and buy contracts to
 </t>
         </is>
       </c>
@@ -8616,42 +8620,42 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>09-11</t>
+          <t>09-12</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">### mon?s4
-  ,z ! fl{}s grew 9
-popul&gt;;y1 pr(es.nal
-gr{}s pd hi&lt;} &amp; hi&lt;}
-prices = bulbs ) !
-virus4 ,by sixte5
-?irty-f|r1 9 "p z a
-result ( dem&amp; f ! ,fr5*1
-speculators 2gan to 5t}
-! m&gt;ket4 ,9 sixte5
-?irty-six1 ! ,dut* cr1t$
+          <t xml:space="preserve">### buy bulbs at ! 5d ( !
+s1son4 ,trad}s met at
+tav}ns1 &amp; buy}s 7
+requir$ to pay a fee p}
+trade4 ,p 7 pur*as+
+bulbs at hi&lt;} &amp; hi&lt;}
+prices1 9t5d+ to resell
+!m = a pr(it4
+  ,h{"e1 s* a s*eme cd n
+la/ un.s "s"o 0
+ultimately will+ to pay
 </t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">months.
-  As the flowers grew in
-popularity, professional
-growers paid higher and higher
-prices for bulbs with the
-virus. By sixteen
-thirty-four, in part as a
-result of demand from the French,
-speculators began to enter
-the market. In sixteen
-thirty-six, the Dutch created
+          <t xml:space="preserve">buy bulbs at the end of the
+season. Traders met at
+taverns, and buyers were
+required to pay a fee per
+trade. People were purchasing
+bulbs at higher and higher
+prices, intending to resell
+them for a profit.
+  However, such a scheme could not
+last unless someone was
+ultimately willing to pay
 </t>
         </is>
       </c>
@@ -8663,509 +8667,429 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>09-12</t>
+          <t>09-13</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">### a type ( =mal futures
-m&gt;kets : m}*ants us$ to
-sell &amp; buy 3tracts to
-buy bulbs at ! 5d ( !
-s1son4 ,trad}s met at
-tav}ns &amp; buy}s 7 requir$
-to pay a fee p} trade4
-,p 7 pur*as+ bulbs at
-hi&lt;} &amp; hi&lt;} prices1
-9t5d+ to re-sell !m = a
-pr(it4
-</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a type of formal futures
-markets which merchants used to
-sell and buy contracts to
-buy bulbs at the end of the
-season. Traders met at
-taverns and buyers were required
-to pay a fee per trade.
-People were purchasing bulbs at
-higher and higher prices,
-intending to re-sell them for a
-profit.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>13</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>09-13</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">###   ,h{"e1 s* a s*eme cd n
-la/ un.s "s"o 0
-ultimately will+ to pay
-s* hi&lt; prices &amp; take
+          <t xml:space="preserve">### s* hi&lt; prices &amp; take
 posses.n ( ! bulbs4 ,9
-,febru&gt;y sixte5
-?irty-sev51 tulip trad}s
-cd no l;g} f9d new buy}s
-will+ to pay 9cr1s+ly
-9flat$ prices = _!
-bulbs4 ,z ? r1liza;n set
-</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  However, such a scheme could not
-last unless someone was
-ultimately willing to pay
-such high prices and take
-possession of the bulbs. In
-February sixteen
-thirty-seven, tulip traders
-could no longer find new buyers
-willing to pay increasingly
-inflated prices for their
-bulbs. As this realization set
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>14</v>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>09-14</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### in1 ! dem&amp; = tulips
+,febru&gt;y #afcg1 tulip
+trad}s cd no l;g} f9d
+new buy}s will+ to pay
+9cr1s+ly 9flat$ prices =
+_! bulbs4 ,z ? r1liza;n
+set in1 ! dem&amp; = tulips
 collaps$1 &amp; prices
 plummet$4 ,! speculative
 bu2le bur/4 ,"s 7 left
-hold+ 3tracts to pur*ase
+</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">such high prices and take
+possession of the bulbs. In
+February 1637, tulip
+traders could no longer find
+new buyers willing to pay
+increasingly inflated prices for
+their bulbs. As this realization
+set in, the demand for tulips
+collapsed, and prices
+plummeted. The speculative
+bubble burst. Some were left
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>14</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>09-14</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### hold+ 3tracts to pur*ase
 tulips at prices n{ t5
 "ts grt} ?an ~? on ! op5
 m&gt;ket1 :ile o!rs f.d
 !mvs 9 posses.n ( bulbs
 n{ wor? a frac;n ( !
 price !y _h pd4
-</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">in, the demand for tulips
-collapsed, and prices
-plummeted. The speculative
-bubble burst. Some were left
-holding contracts to purchase
+  ,! ev5t 0 popul&gt;iz$ 9
+#ahda by ! book
+,extraord9&gt;y ,popul&gt;
+,delu.ns &amp; ! ,mad;s (
+</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holding contracts to purchase
 tulips at prices now ten
 times greater than those on the open
 market, while others found
 themselves in possession of bulbs
 now worth a fraction of the
 price they had paid.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+  The event was popularized in
+1841 by the book
+Extraordinary Popular
+Delusions and the Madness of
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B182" t="n">
+      <c r="B181" t="n">
         <v>15</v>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>09-15</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">###   ,! ev5t 0 popul&gt;iz$ 9
-ei&lt;te5 =ty-"o by ! book
-,extraord9&gt;y ,popul&gt;
-,delu.ns &amp; ! ,mad;s (
-,cr{ds1 t a ,briti%
+      <c r="D181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### ,cr{ds t a ,briti%
 j|rnali/ ,*&gt;les ,mackay
 wrote4 ,t cr{ds ( p (t5
 2have irra;nally 0 ! ma9
 !sis ( ! book1 &amp; tulip
 mania 0 "o ( ! prim&gt;y
 examples4 ,ac to
-</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  The event was popularized in
-eighteen forty-one by the book
-Extraordinary Popular
-Delusions and the Madness of
-Crowds, that a British
+,mackay1 at "o po9t
+twelve acres ( l&amp; 7 (f}$
+= a ,semp} ,augu/us
+bulb4 ,he claims t _m s*
+</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crowds that a British
 journalist Charles Mackay
 wrote. That crowds of people often
 behave irrationally was the main
 thesis of the book, and tulip
 mania was one of the primary
 examples. According to
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+Mackay, at one point
+twelve acres of land were offered
+for a Semper Augustus
+bulb. He claims that many such
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B183" t="n">
+      <c r="B182" t="n">
         <v>16</v>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>09-16</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### ,mackay1 at "o po9t
-twelve acres ( l&amp; 7 (f}$
-= a ,semp} ,augu/us
-bulb4 ,he claims t _m s*
-9ve/ors ru9$ by ! fall 9
-prices 7 desp}ate1 &amp;
+      <c r="D182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### 9ve/ors1 ru9$ by ! fall
+9 prices1 7 desp}ate1 &amp;
 ,dut* comm}ce su6}$ a
 sev}e %ock4 ,9 ,mackay's
 a3.t1 ! panick$ tulip
 speculators s"| help f !
 gov}n;t ( ! ,ne!rl&amp;s1 :
-</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mackay, at one point
-twelve acres of land were offered
-for a Semper Augustus
-bulb. He claims that many such
-investors ruined by the fall in
-prices were desperate, and
+respond$ by dclg t any"o
+:o _h b"| 3tracts to
+pur*ase bulbs 9 ! future
+cd void _! 3tract by
+</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">investors, ruined by the fall
+in prices, were desperate, and
 Dutch commerce suffered a
 severe shock. In Mackay's
 account, the panicked tulip
 speculators sought help from the
 government of the Netherlands, which
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+responded by declaring that anyone
+who had bought contracts to
+purchase bulbs in the future
+could void their contract by
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B184" t="n">
+      <c r="B183" t="n">
         <v>17</v>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>09-17</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### respond$ by dclg t any"o
-:o _h b"| 3tracts to
-pur*ase bulbs 9 ! future
-cd void _! 3tract by
-pay;t ( a t5 p}c5t fee4
+      <c r="D183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### pay;t ( a t5 p}c5t fee4
 ,attempts t 7 made to
 resolve ! situa;n to !
 satisfac;n ( all "pies 7
 unsu3ess;l4 ,! mania
 f9ally 5d$1 ,mackay
 says1 ) 9dividuals /uck
-</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">responded by declaring that anyone
-who had bought contracts to
-purchase bulbs in the future
-could void their contract by
-payment of a ten percent fee.
+) ! bulbs !y held at !
+5d ( ! cra%4 ,no c|rt wd
+5=ce pay;t ( a 3tract1
+s9ce judges reg&gt;d$ !
+</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">payment of a ten percent fee.
 Attempts that were made to
 resolve the situation to the
 satisfaction of all parties were
 unsuccessful. The mania
 finally ended, Mackay
 says, with individuals stuck
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+with the bulbs they held at the
+end of the crash. No court would
+enforce payment of a contract,
+since judges regarded the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B185" t="n">
+      <c r="B184" t="n">
         <v>18</v>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>09-18</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### ) ! bulbs !y held at !
-5d ( ! cra%4 ,no c|rt wd
-5=ce pay;t ( a 3tract1
-s9ce judges reg&gt;d$ !
-debts z 3tract$ "?
+      <c r="D184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### debts z 3tract$ "?
 gambl+1 &amp; ?us n 5=c1ble
 by law4
   ,al? ,mackay's book is
 a classic t _m publi%+
 h|ses 3t9ue repr9t+ td1
 8 a3.t is 3te/$4 ,_m
-</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">with the bulbs they held at the
-end of the crash. No court would
-enforce payment of a contract,
-since judges regarded the
-debts as contracted through
+mod}n s*ol&gt;s 2lieve !
+mania 0 n z extraord9&gt;y
+z ,mackay describ$1 ) "s
+&gt;gu+ t ! price *anges
+</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">debts as contracted through
 gambling, and thus not enforceable
 by law.
   Although Mackay's book is
 a classic that many publishing
 houses continue reprinting today,
 his account is contested. Many
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>19</v>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>09-19</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### mod}n s*ol&gt;s 2lieve !
-mania 0 n z extraord9&gt;y
-z ,mackay describ$1 ) "s
-&gt;gu+ t ! price *anges
-may n h 3/itut$ a bu2le4
-,rese&gt;* on ! tulip mania
-is di6icult 2c ( !
-limit$ data f ! sixte5
-?irties4 ,h{"e1 "s mod}n
-economi/s h propos$
-ra;nal explana;ns1 r ?an
-</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t xml:space="preserve">modern scholars believe the
+modern scholars believe the
 mania was not as extraordinary
 as Mackay described, with some
 arguing that the price changes
-may not have constituted a bubble.
-Research on the tulip mania
-is difficult because of the
-limited data from the sixteen
-thirties. However, some modern
-economists have proposed
-rational explanations, rather than
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B187" t="n">
-        <v>20</v>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>09-20</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### a speculative mania1 = !
+      <c r="B185" t="n">
+        <v>19</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>09-19</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### may n h 3/itut$ a bu2le4
+  ,rese&gt;* on ! tulip
+mania is di6icult 2c ( !
+limit$ data f ! #afcjs4
+,h{"e1 "s mod}n
+economi/s h propos$
+ra;nal explana;ns1 r ?an
+a speculative mania1 = !
 rise &amp; fall 9 prices4 ,=
 example1 o!r fl{}s1 s* z
 ! hyac9?1 al _h hi&lt;
-prices on ! fl{}'s
+</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">may not have constituted a bubble.
+  Research on the tulip
+mania is difficult because of the
+limited data from the 1630s.
+However, some modern
+economists have proposed
+rational explanations, rather than
+a speculative mania, for the
+rise and fall in prices. For
+example, other flowers, such as
+the hyacinth, also had high
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>20</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>09-20</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### prices on ! fl{}'s
 9troduc;n1 : !n fell
 dramatically4 ,! hi&lt;
 prices may al h be5
 driv5 by expecta;ns ( a
 p&gt;lia;t&gt;y decree t
 3tracts cd 2 void$ = a
-</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t xml:space="preserve">a speculative mania, for the
-rise and fall in prices. For
-example, other flowers, such as
-the hyacinth, also had high
-prices on the flower's
+small co/1 ?us l{}+ !
+risk to buy}s4 ,despite
+~! 4agree;ts ab :e!r !
+ph5om5on te*nically
+</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prices on the flower's
 introduction, which then fell
 dramatically. The high
 prices may also have been
 driven by expectations of a
 parliamentary decree that
 contracts could be voided for a
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
+small cost, thus lowering the
+risk to buyers. Despite
+these disagreements about whether the
+phenomenon technically
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B188" t="n">
+      <c r="B187" t="n">
         <v>21</v>
       </c>
-      <c r="C188" t="inlineStr">
+      <c r="C187" t="inlineStr">
         <is>
           <t>09-21</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### small co/1 ?us l{}+ !
-risk to buy}s4 ,despite
-~! 4agree;ts ab :e!r !
-ph5om5on te*nically
-3/itut$ an economic
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>### 3/itut$ an economic
 bu2le1 ! t}m 8tulip
 mania0 is / (t5 us$
 metaphorically to ref}
 to any l&gt;ge economic
 bu2le1 :5 asset prices
 deviate f 9tr9sic
-</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">small cost, thus lowering the
-risk to buyers. Despite
-these disagreements about whether the
-phenomenon technically
-constituted an economic
+values4</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>constituted an economic
 bubble, the term "tulip
 mania" is still often used
 metaphorically to refer
 to any large economic
 bubble, when asset prices
 deviate from intrinsic
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>22</v>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>09-22</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>### values4</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
+values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B190" t="n">
+      <c r="B188" t="n">
         <v>1</v>
       </c>
-      <c r="C190" t="inlineStr">
+      <c r="C188" t="inlineStr">
         <is>
           <t>10-01</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t xml:space="preserve">###   ,t|rette's syndrome1 a
 neurological 4ord} "*iz$
@@ -9175,13 +9099,13 @@
 ,t|rette1 ! pione}+
 ,fr5* neurologi/ :o f/
 describ$ ! 3di;n 9 an
-ei&lt;ty-six-ye&gt;-old ,fr5*
+#hf-ye&gt;-old ,fr5*
 noblewoman4 ,x is alm
 alw 9 *ildhood t ! e&gt;ly
 </t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t xml:space="preserve">  Tourette's syndrome, a
 neurological disorder characterized
@@ -9191,122 +9115,122 @@
 Tourette, the pioneering
 French neurologist who first
 described the condition in an
-eighty-six-year-old French
+86-year-old French
 noblewoman. It is almost
 always in childhood that the early
 </t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B191" t="n">
+      <c r="B189" t="n">
         <v>2</v>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C189" t="inlineStr">
         <is>
           <t>10-02</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t xml:space="preserve">### symptoms ( ,t|rette's &gt;e
 f/ notic$1 ) ! av}age
 onset 2t ! ages ( sev5 &amp;
 t5 ye&gt;s4 ,x is e/imat$ t
-two hundr$ ?|s&amp;
-,am}icans h ! mo/ sev}e
-=m ( ,t|rette's1 &amp; z _m
-z "o 9 a hundr$ p
-exhibit mild} &amp; less
-complex symptoms t
-9clude *ronic motor &amp;
-</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
+#bjj1jjj ,am}icans h !
+mo/ sev}e =m (
+,t|rette's1 &amp; z _m z "o
+9 a hundr$ p exhibit
+mild} &amp; less complex
+symptoms t 9clude *ronic
+motor &amp; vocal tics or
+</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
         <is>
           <t xml:space="preserve">symptoms of Tourette's are
 first noticed, with the average
 onset between the ages of seven and
 ten years. It is estimated that
-two hundred thousand
-Americans have the most severe
-form of Tourette's, and as many
-as one in a hundred people
-exhibit milder and less
-complex symptoms that
-include chronic motor and
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
+200,jjj Americans have the
+most severe form of
+Tourette's, and as many as one
+in a hundred people exhibit
+milder and less complex
+symptoms that include chronic
+motor and vocal tics or
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B192" t="n">
+      <c r="B190" t="n">
         <v>3</v>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="C190" t="inlineStr">
         <is>
           <t>10-03</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### vocal tics or transi5t
-tics ( *ildhood4 ,= !
-major;y ( p diagnos$ ) !
-4ord}1 ,t|rette's is n a
-*ronic 3di;n ) symptoms
-la/+ a life"t4 ,r x is a
-3di;n ~: sev};y p1ks 9 !
-e&gt;ly te5s1 ) improve;t
-o3urr+ 9 ! late te5s &amp;
-3t9u+ 9to adulthood4
+      <c r="D190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### transi5t tics (
+*ildhood4 ,= ! major;y (
+p diagnos$ ) ! 4ord}1
+,t|rette's is n a *ronic
+3di;n ) symptoms la/+ a
+life"t4 ,r1 x is a 3di;n
+~: sev};y p1ks 9 ! e&gt;ly
+te5s1 ) improve;t o3urr+
+9 ! late te5s &amp; 3t9u+
+9to adulthood4
   ,h{"e1 approximately
 </t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vocal tics or transient
-tics of childhood. For the
-majority of people diagnosed with the
-disorder, Tourette's is not a
-chronic condition with symptoms
-lasting a lifetime. Rather it is a
-condition whose severity peaks in the
-early teens, with improvement
-occurring in the late teens and
-continuing into adulthood.
+      <c r="E190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">transient tics of
+childhood. For the majority of
+people diagnosed with the disorder,
+Tourette's is not a chronic
+condition with symptoms lasting a
+lifetime. Rather, it is a condition
+whose severity peaks in the early
+teens, with improvement occurring
+in the late teens and continuing
+into adulthood.
   However, approximately
 </t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B193" t="n">
+      <c r="B191" t="n">
         <v>4</v>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C191" t="inlineStr">
         <is>
           <t>10-04</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D191" t="inlineStr">
         <is>
           <t xml:space="preserve">### t5 p}c5t ( ~? a6ect$ h a
 progressive or 4abl+
@@ -9316,13 +9240,13 @@
 pres5t = an ext5d$ p}iod
 ( "t 2f a =mal diagnosis
 ( ,t|rette's is obta9$4
-,! r1sons = ? &gt;e _m &amp;
+,! r1sons = ? &gt;e _m1 &amp;
 may 9clude ! fact t =
 families &amp; physicians
 </t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E191" t="inlineStr">
         <is>
           <t xml:space="preserve">ten percent of those affected have a
 progressive or disabling
@@ -9332,28 +9256,28 @@
 present for an extended period
 of time before a formal diagnosis
 of Tourette's is obtained.
-The reasons for this are many and
+The reasons for this are many, and
 may include the fact that for
 families and physicians
 </t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B194" t="n">
+      <c r="B192" t="n">
         <v>5</v>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="C192" t="inlineStr">
         <is>
           <t>10-05</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D192" t="inlineStr">
         <is>
           <t xml:space="preserve">### unfamili&gt; ) ,t|rette's1
 mild &amp; ev5 mod}ate tic
@@ -9369,7 +9293,7 @@
 </t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E192" t="inlineStr">
         <is>
           <t xml:space="preserve">unfamiliar with Tourette's,
 mild and even moderate tic
@@ -9386,21 +9310,21 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B195" t="n">
+      <c r="B193" t="n">
         <v>6</v>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C193" t="inlineStr">
         <is>
           <t>10-06</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t xml:space="preserve">### pati5ts :o &gt;e
 self-diagnos$ af !y1 _!
@@ -9416,7 +9340,7 @@
 </t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E193" t="inlineStr">
         <is>
           <t xml:space="preserve">patients who are
 self-diagnosed after they, their
@@ -9433,21 +9357,21 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B196" t="n">
+      <c r="B194" t="n">
         <v>7</v>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C194" t="inlineStr">
         <is>
           <t>10-07</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t xml:space="preserve">### gr|ps4 ,"s ( ! m common
 simple tics 9clude eye
@@ -9458,12 +9382,12 @@
 tics typically prec$e1
 mi&lt;t 9clude repetitive
 ?roat-cle&gt;+1 sni6+1 or
-grunt+ s.ds4 ,complex
-tics &gt;e 4t9ct1 coord9at$
-</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
+grunt+ s.ds4
+  ,complex tics &gt;e
+</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
         <is>
           <t xml:space="preserve">groups. Some of the more common
 simple tics include eye
@@ -9474,52 +9398,52 @@
 tics typically precede,
 might include repetitive
 throat-clearing, sniffing, or
-grunting sounds. Complex
-tics are distinct, coordinated
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+grunting sounds.
+  Complex tics are
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B197" t="n">
+      <c r="B195" t="n">
         <v>8</v>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>10-08</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### patt}ns ( move;t t
-9volve s"eal muscle
-gr|ps4 ,complex motor
-tics mi&lt;t 9clude facial
-grimac+ comb9$ ) a h1d
-twi/ &amp; a %|ld} %rug4
-,o!r complex motor tics
-may actually appe&gt;
+      <c r="D195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### 4t9ct1 coord9at$ patt}ns
+( move;t t 9volve s"eal
+muscle gr|ps4 ,complex
+motor tics mi&lt;t 9clude
+facial grimac+ comb9$ )
+a h1d twi/ &amp; a %|ld}
+%rug4 ,o!r complex motor
+tics may actually appe&gt;
 purpose;l1 9clud+ sni6+
 or t|*+ objects1 hopp+1
 jump+1 b5d+1 or twi/+4
 </t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">patterns of movement that
-involve several muscle
-groups. Complex motor
-tics might include facial
-grimacing combined with a head
-twist and a shoulder shrug.
-Other complex motor tics
-may actually appear
+      <c r="E195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">distinct, coordinated patterns
+of movement that involve several
+muscle groups. Complex
+motor tics might include
+facial grimacing combined with
+a head twist and a shoulder
+shrug. Other complex motor
+tics may actually appear
 purposeful, including sniffing
 or touching objects, hopping,
 jumping, bending, or twisting.
@@ -9527,28 +9451,28 @@
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+    <row r="196">
+      <c r="A196" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B198" t="n">
+      <c r="B196" t="n">
         <v>9</v>
       </c>
-      <c r="C198" t="inlineStr">
+      <c r="C196" t="inlineStr">
         <is>
           <t>10-09</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D196" t="inlineStr">
         <is>
           <t xml:space="preserve">### ,complex vocal tics
 9clude ~ws or phrases4
 ,p}h ! mo/ dramatic &amp;
 4abl+ tics 9clude motor
 move;ts t result 9
-self-h&gt;m s* z pun*+ "of
+self-h&gt;m1 s* z pun*+ "of
 9 ! face or vocal tics
 9clud+ coprolalia1 :
 9volves utt}+ swe&gt; ~ws1
@@ -9557,14 +9481,14 @@
 </t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E196" t="inlineStr">
         <is>
           <t xml:space="preserve">Complex vocal tics
 include words or phrases.
 Perhaps the most dramatic and
 disabling tics include motor
 movements that result in
-self-harm such as punching oneself
+self-harm, such as punching oneself
 in the face or vocal tics
 including coprolalia, which
 involves uttering swear words,
@@ -9574,73 +9498,73 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+    <row r="197">
+      <c r="A197" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B199" t="n">
+      <c r="B197" t="n">
         <v>10</v>
       </c>
-      <c r="C199" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>10-10</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### ( o!rs4 ,tics &gt;e (t5
-worse ) excite;t or
-anxiety &amp; bett} dur+
-calm1 focus$ activities4
-,c}ta9 physical exp}i;es
-c tri7} or wors5 tics4
-,= example1 ti&lt;t coll&gt;s
-may tri7} neck tics1 or
-he&gt;+ ano!r p}son sniff
-or ?roat-cle&gt; may tri7}
-! produc;n ( simil&gt;
-</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t xml:space="preserve">of others. Tics are often
-worse with excitement or
-anxiety and better during
-calm, focused activities.
-Certain physical experiences
-can trigger or worsen tics.
-For example, tight collars
-may trigger neck tics, or
-hearing another person sniff
-or throat-clear may trigger
-the production of similar
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="D197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### ( o!rs4
+  ,tics &gt;e (t5 worse )
+excite;t or anxiety &amp;
+bett} dur+ calm1 focus$
+activities4 ,c}ta9
+physical exp}i;es c
+tri7} or wors5 tics4 ,=
+example1 ti&lt;t coll&gt;s may
+tri7} neck tics1 or he&gt;+
+ano!r p}son sniff or
+?roat-cle&gt; may tri7} !
+</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">of others.
+  Tics are often worse with
+excitement or anxiety and
+better during calm, focused
+activities. Certain
+physical experiences can
+trigger or worsen tics. For
+example, tight collars may
+trigger neck tics, or hearing
+another person sniff or
+throat-clear may trigger the
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B200" t="n">
+      <c r="B198" t="n">
         <v>11</v>
       </c>
-      <c r="C200" t="inlineStr">
+      <c r="C198" t="inlineStr">
         <is>
           <t>10-11</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">### s.ds4 ,tics come &amp; g ov}
-"t1 v&gt;y+ 9 type1
-frequ5cy1 loca;n1 &amp;
-sev};y4
+      <c r="D198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">### produc;n ( simil&gt; s.ds4
+,tics come &amp; g ov} "t1
+v&gt;y+ 9 type1 frequ5cy1
+loca;n1 &amp; sev};y4
   ,! f/ symptoms
 ,t|rette's pati5ts
 exp}i;e usually o3ur 9 !
@@ -9651,12 +9575,12 @@
 </t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sounds. Tics come and go over
-time, varying in type,
-frequency, location, and
-severity.
+      <c r="E198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">production of similar sounds.
+Tics come and go over time,
+varying in type, frequency,
+location, and severity.
   The first symptoms
 Tourette's patients
 experience usually occur in the
@@ -9668,21 +9592,21 @@
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B201" t="n">
+      <c r="B199" t="n">
         <v>12</v>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="C199" t="inlineStr">
         <is>
           <t>10-12</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t xml:space="preserve">### ( ,t|rette's &gt;e
 9volunt&gt;y1 b "! &gt;e "s p
@@ -9698,7 +9622,7 @@
 </t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E199" t="inlineStr">
         <is>
           <t xml:space="preserve">of Tourette's are
 involuntary, but there are some people
@@ -9715,21 +9639,21 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B202" t="n">
+      <c r="B200" t="n">
         <v>13</v>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C200" t="inlineStr">
         <is>
           <t>10-13</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t xml:space="preserve">### feel t ! tic m/ 2
 express$4 ,tics 9
@@ -9741,11 +9665,11 @@
 exp}i;e addi;nal
 neurobehavioral problems
 t 9clude 9att5;n1
-hyp}activ;y &amp;
-</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
+hyp}activ;y1 &amp;
+</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
         <is>
           <t xml:space="preserve">feel that the tic must be
 expressed. Tics in
@@ -9757,26 +9681,26 @@
 experience additional
 neurobehavioral problems
 that include inattention,
-hyperactivity and
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+hyperactivity, and
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B203" t="n">
+      <c r="B201" t="n">
         <v>14</v>
       </c>
-      <c r="C203" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t>10-14</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t xml:space="preserve">### impulsiv;y4 ,p )
 ,t|rette's h al report$
@@ -9785,14 +9709,14 @@
 o!r di6iculties
 ,t|rette's syndrome may
 or may n directly cause4
-,t|rette's is a
+  ,t|rette's is a
 diagnosis doctors make
 af v}ify+ t ! pati5t has
 _h bo? motor &amp; vocal
 </t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E201" t="inlineStr">
         <is>
           <t xml:space="preserve">impulsivity. People with
 Tourette's have also reported
@@ -9801,7 +9725,7 @@
 other difficulties
 Tourette's syndrome may
 or may not directly cause.
-Tourette's is a
+  Tourette's is a
 diagnosis doctors make
 after verifying that the patient has
 had both motor and vocal
@@ -9809,21 +9733,21 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="202">
+      <c r="A202" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B204" t="n">
+      <c r="B202" t="n">
         <v>15</v>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="C202" t="inlineStr">
         <is>
           <t>10-15</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t xml:space="preserve">### tics = at l1/ "o ye&gt;4 ,!
 exi/;e ( o!r
@@ -9839,7 +9763,7 @@
 </t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E202" t="inlineStr">
         <is>
           <t xml:space="preserve">tics for at least one year. The
 existence of other
@@ -9856,26 +9780,26 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B205" t="n">
+      <c r="B203" t="n">
         <v>16</v>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>10-16</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t xml:space="preserve">### symptoms or atypical
-pres5ta;n s* z onset (
-symptoms 9 adulthood may
-require specialty
+pres5ta;n1 s* z onset (
+symptoms 9 adulthood1
+may require specialty
 exp}tise = diagnosis4
 ,"! &gt;e no blood or
 laboratory te/s ne$$ =
@@ -9886,12 +9810,12 @@
 </t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E203" t="inlineStr">
         <is>
           <t xml:space="preserve">symptoms or atypical
-presentation such as onset of
-symptoms in adulthood may
-require specialty
+presentation, such as onset of
+symptoms in adulthood,
+may require specialty
 expertise for diagnosis.
 There are no blood or
 laboratory tests needed for
@@ -9903,25 +9827,25 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B206" t="n">
+      <c r="B204" t="n">
         <v>17</v>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C204" t="inlineStr">
         <is>
           <t>10-17</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t xml:space="preserve">### tomography1 &amp;
 electro5cephalograms1 z
-well z c}ta9 lab te/s
+well z c}ta9 lab te/s1
 may 2 us$ to rule | o!r
 3di;ns t ,t|rette's mi&lt;t
 2 3fus$ )4
@@ -9933,11 +9857,11 @@
 </t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t xml:space="preserve">tomography, and
 electroencephalograms, as
-well as certain lab tests
+well as certain lab tests,
 may be used to rule out other
 conditions that Tourette's might
 be confused with.
@@ -9950,21 +9874,21 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="205">
+      <c r="A205" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B207" t="n">
+      <c r="B205" t="n">
         <v>18</v>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>10-18</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t xml:space="preserve">### e&gt;ly family /udies
 su7e/$ an autosomal
@@ -9980,7 +9904,7 @@
 </t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t xml:space="preserve">early family studies
 suggested an autosomal
@@ -9997,26 +9921,26 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+    <row r="206">
+      <c r="A206" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B208" t="n">
+      <c r="B206" t="n">
         <v>19</v>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>10-19</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t xml:space="preserve">### play a role 9 !
 develop;t ( ,t|rette's4
-,g5etic /udies al su7e/
-t "s =ms ( ,att5;n
+  ,g5etic /udies al
+su7e/ t "s =ms ( ,att5;n
 ,deficit ,hyp}activ;y
 ,4ord} &amp; ,obsessive
 ,compulsive ,4ord} &gt;e
@@ -10027,12 +9951,12 @@
 </t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E206" t="inlineStr">
         <is>
           <t xml:space="preserve">play a role in the
 development of Tourette's.
-Genetic studies also suggest
-that some forms of Attention
+  Genetic studies also
+suggest that some forms of Attention
 Deficit Hyperactivity
 Disorder and Obsessive
 Compulsive Disorder are
@@ -10044,21 +9968,21 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+    <row r="207">
+      <c r="A207" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B209" t="n">
+      <c r="B207" t="n">
         <v>20</v>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>10-20</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t xml:space="preserve">### &amp; o!r neurobehavioral
 problems t ,t|rette's
@@ -10068,13 +9992,13 @@
 is play$ by ! sex ( !
 p}son4 ,9 "picul&gt;1 males
 a6ect$ by ! g5e &gt;e m
-likely to h tics &amp;
+likely to h tics1 &amp;
 females :o h a g5etic
 pr$isposi;n &gt;e m likely
 </t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t xml:space="preserve">and other neurobehavioral
 problems that Tourette's
@@ -10084,28 +10008,28 @@
 is played by the sex of the
 person. In particular, males
 affected by the gene are more
-likely to have tics and
+likely to have tics, and
 females who have a genetic
 predisposition are more likely
 </t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+    <row r="208">
+      <c r="A208" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B210" t="n">
+      <c r="B208" t="n">
         <v>21</v>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>10-21</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t xml:space="preserve">### to h
 obsessive-compulsive
@@ -10121,7 +10045,7 @@
 </t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t xml:space="preserve">to have
 obsessive-compulsive
@@ -10138,26 +10062,26 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B211" t="n">
+      <c r="B209" t="n">
         <v>22</v>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>10-22</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>### tr1t;ts = ,t|rette's4</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E209" t="inlineStr">
         <is>
           <t>treatments for Tourette's.</t>
         </is>
